--- a/assets/xlsx/links.xlsx
+++ b/assets/xlsx/links.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18750" windowHeight="10650"/>
+    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="400"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$50</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="256">
   <si>
     <t>站序</t>
   </si>
@@ -795,84 +798,6 @@
   </si>
   <si>
     <t>官网,https://v.qq.com</t>
-  </si>
-  <si>
-    <t>超长网站名称测试｜这是一个特别特别长的网站名称用来验证标题行截断省略号效果是否正常</t>
-  </si>
-  <si>
-    <t>正常长度的描述文字</t>
-  </si>
-  <si>
-    <t>搜索,测试</t>
-  </si>
-  <si>
-    <t>官网,https://www.baidu.com;百度地图,https://map.baidu.com</t>
-  </si>
-  <si>
-    <t>长描述测试站</t>
-  </si>
-  <si>
-    <t>这是一段超长的描述文字，用来验证描述行在窄卡片中的截断省略号效果：它包含大量修饰语、从句与标点符号，确保在手机两列、平板三列、桌面四列的卡片宽度下都不会把卡片撑高，而是安静地截断为一行省略号。</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>AI,测试,长文本</t>
-  </si>
-  <si>
-    <t>多标签测试站</t>
-  </si>
-  <si>
-    <t>标签按钮特别多的测试卡片</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx51/640/396</t>
-  </si>
-  <si>
-    <t>设计,UI,UX,插画,品牌,海报,字体,配色,灵感,摄影,三维,动效,测试</t>
-  </si>
-  <si>
-    <t>多链接测试站</t>
-  </si>
-  <si>
-    <t>链接标签特别多的测试卡片</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx52/640/396</t>
-  </si>
-  <si>
-    <t>视频,测试</t>
-  </si>
-  <si>
-    <t>官网,https://www.bilibili.com;知乎,https://www.zhihu.com;小红书,https://www.xiaohongshu.com;百度,https://www.baidu.com;Google,https://www.google.com;微博,https://weibo.com;豆瓣,https://www.douban.com;B站,https://www.bilibili.com</t>
-  </si>
-  <si>
-    <t>全维度超长测试：名称描述标签链接全部超长的纵向封面卡片</t>
-  </si>
-  <si>
-    <t>这是为纵向封面卡片准备的超长描述：纵向卡片更窄、文本行更容易超出，正好用于综合验证名称截断、描述截断、标签横滚与链接横滚四种行为同时生效的效果。</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx53/396/640</t>
-  </si>
-  <si>
-    <t>开发,前端,后端,算法,运维,数据库,云原生,测试</t>
-  </si>
-  <si>
-    <t>官网,https://github.com;知乎,https://www.zhihu.com;百度,https://www.baidu.com;Google,https://www.google.com;掘金,https://juejin.cn;V2EX,https://www.v2ex.com</t>
-  </si>
-  <si>
-    <t>全维度超长测试（无图片占位版）：名称描述标签链接全部超长</t>
-  </si>
-  <si>
-    <t>名称、描述、标签、链接全部超长且不配置图片的测试卡片，用于同时验证文字 logo 占位与各行内容超出截断/横滚行为的组合效果。</t>
-  </si>
-  <si>
-    <t>学习,课程,百科,词典,测试,免费,在线,高校</t>
-  </si>
-  <si>
-    <t>官网,https://www.icourse163.org;知乎,https://www.zhihu.com;百度,https://www.baidu.com;Google,https://www.google.com;微博,https://weibo.com</t>
   </si>
 </sst>
 </file>
@@ -1486,10 +1411,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1836,17 +1760,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16.75" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="52" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="90" customWidth="1"/>
+    <col min="6" max="6" width="50.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="8" width="32.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1865,13 +1789,13 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1894,7 +1818,7 @@
       <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1914,13 +1838,13 @@
       <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1940,13 +1864,13 @@
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1966,13 +1890,13 @@
       <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G5" t="s">
         <v>27</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1992,13 +1916,13 @@
       <c r="E6" t="s">
         <v>30</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>31</v>
       </c>
       <c r="G6" t="s">
         <v>32</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2018,13 +1942,13 @@
       <c r="E7" t="s">
         <v>35</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>36</v>
       </c>
       <c r="G7" t="s">
         <v>37</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2044,13 +1968,13 @@
       <c r="E8" t="s">
         <v>40</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="1" t="s">
         <v>41</v>
       </c>
       <c r="G8" t="s">
         <v>42</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="1" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2070,13 +1994,13 @@
       <c r="E9" t="s">
         <v>46</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G9" t="s">
         <v>48</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="1" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2096,13 +2020,13 @@
       <c r="E10" t="s">
         <v>51</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="1" t="s">
         <v>52</v>
       </c>
       <c r="G10" t="s">
         <v>53</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="1" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2125,7 +2049,7 @@
       <c r="G11" t="s">
         <v>57</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="1" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2148,7 +2072,7 @@
       <c r="G12" t="s">
         <v>61</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="1" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2168,13 +2092,13 @@
       <c r="E13" t="s">
         <v>64</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="1" t="s">
         <v>65</v>
       </c>
       <c r="G13" t="s">
         <v>66</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="1" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2194,13 +2118,13 @@
       <c r="E14" t="s">
         <v>69</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="1" t="s">
         <v>70</v>
       </c>
       <c r="G14" t="s">
         <v>71</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="1" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2220,13 +2144,13 @@
       <c r="E15" t="s">
         <v>75</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="1" t="s">
         <v>76</v>
       </c>
       <c r="G15" t="s">
         <v>77</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2246,13 +2170,13 @@
       <c r="E16" t="s">
         <v>80</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="1" t="s">
         <v>81</v>
       </c>
       <c r="G16" t="s">
         <v>82</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2272,13 +2196,13 @@
       <c r="E17" t="s">
         <v>85</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="1" t="s">
         <v>86</v>
       </c>
       <c r="G17" t="s">
         <v>87</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="1" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2298,13 +2222,13 @@
       <c r="E18" t="s">
         <v>90</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="1" t="s">
         <v>91</v>
       </c>
       <c r="G18" t="s">
         <v>92</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="1" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2324,13 +2248,13 @@
       <c r="E19" t="s">
         <v>95</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="1" t="s">
         <v>96</v>
       </c>
       <c r="G19" t="s">
         <v>97</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="1" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2350,13 +2274,13 @@
       <c r="E20" t="s">
         <v>100</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G20" t="s">
         <v>102</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="1" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2376,13 +2300,13 @@
       <c r="E21" t="s">
         <v>106</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>107</v>
       </c>
       <c r="G21" t="s">
         <v>108</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="1" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2402,13 +2326,13 @@
       <c r="E22" t="s">
         <v>111</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G22" t="s">
         <v>113</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="1" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2428,13 +2352,13 @@
       <c r="E23" t="s">
         <v>116</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="1" t="s">
         <v>117</v>
       </c>
       <c r="G23" t="s">
         <v>118</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="1" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2454,13 +2378,13 @@
       <c r="E24" t="s">
         <v>121</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G24" t="s">
         <v>123</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="1" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2480,13 +2404,13 @@
       <c r="E25" t="s">
         <v>126</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="1" t="s">
         <v>127</v>
       </c>
       <c r="G25" t="s">
         <v>128</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="1" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2506,13 +2430,13 @@
       <c r="E26" t="s">
         <v>131</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="1" t="s">
         <v>132</v>
       </c>
       <c r="G26" t="s">
         <v>133</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="1" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2532,13 +2456,13 @@
       <c r="E27" t="s">
         <v>137</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>138</v>
       </c>
       <c r="G27" t="s">
         <v>139</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="1" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2558,13 +2482,13 @@
       <c r="E28" t="s">
         <v>142</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="1" t="s">
         <v>143</v>
       </c>
       <c r="G28" t="s">
         <v>144</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="1" t="s">
         <v>145</v>
       </c>
     </row>
@@ -2584,13 +2508,13 @@
       <c r="E29" t="s">
         <v>147</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="1" t="s">
         <v>148</v>
       </c>
       <c r="G29" t="s">
         <v>149</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="1" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2610,13 +2534,13 @@
       <c r="E30" t="s">
         <v>152</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>153</v>
       </c>
       <c r="G30" t="s">
         <v>154</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="1" t="s">
         <v>155</v>
       </c>
     </row>
@@ -2636,13 +2560,13 @@
       <c r="E31" t="s">
         <v>157</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G31" t="s">
         <v>159</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="1" t="s">
         <v>160</v>
       </c>
     </row>
@@ -2662,13 +2586,13 @@
       <c r="E32" t="s">
         <v>162</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>163</v>
       </c>
       <c r="G32" t="s">
         <v>164</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="1" t="s">
         <v>165</v>
       </c>
     </row>
@@ -2688,13 +2612,13 @@
       <c r="E33" t="s">
         <v>168</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="1" t="s">
         <v>169</v>
       </c>
       <c r="G33" t="s">
         <v>170</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="1" t="s">
         <v>171</v>
       </c>
     </row>
@@ -2714,13 +2638,13 @@
       <c r="E34" t="s">
         <v>173</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="1" t="s">
         <v>174</v>
       </c>
       <c r="G34" t="s">
         <v>175</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="1" t="s">
         <v>176</v>
       </c>
     </row>
@@ -2740,13 +2664,13 @@
       <c r="E35" t="s">
         <v>178</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="1" t="s">
         <v>179</v>
       </c>
       <c r="G35" t="s">
         <v>180</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="1" t="s">
         <v>181</v>
       </c>
     </row>
@@ -2766,13 +2690,13 @@
       <c r="E36" t="s">
         <v>183</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="1" t="s">
         <v>184</v>
       </c>
       <c r="G36" t="s">
         <v>185</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="1" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2792,13 +2716,13 @@
       <c r="E37" t="s">
         <v>188</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="1" t="s">
         <v>189</v>
       </c>
       <c r="G37" t="s">
         <v>190</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="1" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2818,13 +2742,13 @@
       <c r="E38" t="s">
         <v>193</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="1" t="s">
         <v>194</v>
       </c>
       <c r="G38" t="s">
         <v>195</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="1" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2844,13 +2768,13 @@
       <c r="E39" t="s">
         <v>199</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="1" t="s">
         <v>200</v>
       </c>
       <c r="G39" t="s">
         <v>201</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="1" t="s">
         <v>202</v>
       </c>
     </row>
@@ -2870,13 +2794,13 @@
       <c r="E40" t="s">
         <v>204</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="1" t="s">
         <v>205</v>
       </c>
       <c r="G40" t="s">
         <v>206</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="1" t="s">
         <v>207</v>
       </c>
     </row>
@@ -2896,13 +2820,13 @@
       <c r="E41" t="s">
         <v>209</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="1" t="s">
         <v>210</v>
       </c>
       <c r="G41" t="s">
         <v>211</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="1" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2922,13 +2846,13 @@
       <c r="E42" t="s">
         <v>214</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="1" t="s">
         <v>215</v>
       </c>
       <c r="G42" t="s">
         <v>216</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="1" t="s">
         <v>217</v>
       </c>
     </row>
@@ -2948,13 +2872,13 @@
       <c r="E43" t="s">
         <v>219</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="1" t="s">
         <v>220</v>
       </c>
       <c r="G43" t="s">
         <v>221</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="1" t="s">
         <v>222</v>
       </c>
     </row>
@@ -2977,7 +2901,7 @@
       <c r="G44" t="s">
         <v>225</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" s="1" t="s">
         <v>226</v>
       </c>
     </row>
@@ -2997,13 +2921,13 @@
       <c r="E45" t="s">
         <v>229</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>230</v>
       </c>
       <c r="G45" t="s">
         <v>231</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="1" t="s">
         <v>232</v>
       </c>
     </row>
@@ -3023,13 +2947,13 @@
       <c r="E46" t="s">
         <v>234</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="1" t="s">
         <v>235</v>
       </c>
       <c r="G46" t="s">
         <v>236</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="1" t="s">
         <v>237</v>
       </c>
     </row>
@@ -3049,13 +2973,13 @@
       <c r="E47" t="s">
         <v>239</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="1" t="s">
         <v>240</v>
       </c>
       <c r="G47" t="s">
         <v>241</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="1" t="s">
         <v>242</v>
       </c>
     </row>
@@ -3075,13 +2999,13 @@
       <c r="E48" t="s">
         <v>244</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="1" t="s">
         <v>245</v>
       </c>
       <c r="G48" t="s">
         <v>246</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="1" t="s">
         <v>247</v>
       </c>
     </row>
@@ -3104,7 +3028,7 @@
       <c r="G49" t="s">
         <v>250</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="1" t="s">
         <v>251</v>
       </c>
     </row>
@@ -3124,173 +3048,20 @@
       <c r="E50" t="s">
         <v>253</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="1" t="s">
         <v>254</v>
       </c>
       <c r="G50" t="s">
         <v>250</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
-      <c r="A51">
-        <v>49</v>
-      </c>
-      <c r="B51" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51" t="s">
-        <v>256</v>
-      </c>
-      <c r="E51" t="s">
-        <v>257</v>
-      </c>
-      <c r="F51" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51" t="s">
-        <v>258</v>
-      </c>
-      <c r="H51" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52">
-        <v>50</v>
-      </c>
-      <c r="B52" t="s">
-        <v>44</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52" t="s">
-        <v>260</v>
-      </c>
-      <c r="E52" t="s">
-        <v>261</v>
-      </c>
-      <c r="F52" t="s">
-        <v>262</v>
-      </c>
-      <c r="G52" t="s">
-        <v>263</v>
-      </c>
-      <c r="H52" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53">
-        <v>51</v>
-      </c>
-      <c r="B53" t="s">
-        <v>104</v>
-      </c>
-      <c r="C53">
-        <v>2</v>
-      </c>
-      <c r="D53" t="s">
-        <v>264</v>
-      </c>
-      <c r="E53" t="s">
-        <v>265</v>
-      </c>
-      <c r="F53" t="s">
-        <v>266</v>
-      </c>
-      <c r="G53" t="s">
-        <v>267</v>
-      </c>
-      <c r="H53" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="B54" t="s">
-        <v>227</v>
-      </c>
-      <c r="C54">
-        <v>2</v>
-      </c>
-      <c r="D54" t="s">
-        <v>268</v>
-      </c>
-      <c r="E54" t="s">
-        <v>269</v>
-      </c>
-      <c r="F54" t="s">
-        <v>270</v>
-      </c>
-      <c r="G54" t="s">
-        <v>271</v>
-      </c>
-      <c r="H54" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55">
-        <v>53</v>
-      </c>
-      <c r="B55" t="s">
-        <v>135</v>
-      </c>
-      <c r="C55">
-        <v>3</v>
-      </c>
-      <c r="D55" t="s">
-        <v>273</v>
-      </c>
-      <c r="E55" t="s">
-        <v>274</v>
-      </c>
-      <c r="F55" t="s">
-        <v>275</v>
-      </c>
-      <c r="G55" t="s">
-        <v>276</v>
-      </c>
-      <c r="H55" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="B56" t="s">
-        <v>166</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56" t="s">
-        <v>278</v>
-      </c>
-      <c r="E56" t="s">
-        <v>279</v>
-      </c>
-      <c r="F56" t="s">
-        <v>262</v>
-      </c>
-      <c r="G56" t="s">
-        <v>280</v>
-      </c>
-      <c r="H56" t="s">
-        <v>281</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H50" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" display="中国政协网,http://www.cppcc.gov.cn/"/>
     <hyperlink ref="H3" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>

--- a/assets/xlsx/links.xlsx
+++ b/assets/xlsx/links.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="400"/>
+    <workbookView windowWidth="18990" windowHeight="11235" tabRatio="400"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="304">
   <si>
     <t>站序</t>
   </si>
@@ -71,6 +71,156 @@
     <t>中国政协网,http://www.cppcc.gov.cn/</t>
   </si>
   <si>
+    <t>资讯媒体</t>
+  </si>
+  <si>
+    <t>国际在线</t>
+  </si>
+  <si>
+    <t>中央媒体</t>
+  </si>
+  <si>
+    <t>官网,http://www.cri.cn</t>
+  </si>
+  <si>
+    <t>中国日报网</t>
+  </si>
+  <si>
+    <t>http://www.chinadaily.com.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>官网,http://www.chinadaily.com.cn</t>
+  </si>
+  <si>
+    <t>人民网</t>
+  </si>
+  <si>
+    <t>官网,http://www.people.com.cn/</t>
+  </si>
+  <si>
+    <t>新华网</t>
+  </si>
+  <si>
+    <t>官网,http://www.xinhuanet.com</t>
+  </si>
+  <si>
+    <t>中国军网</t>
+  </si>
+  <si>
+    <t>解放军报社</t>
+  </si>
+  <si>
+    <t>官网,http://www.81.cn/</t>
+  </si>
+  <si>
+    <t>求是网</t>
+  </si>
+  <si>
+    <t>官网,http://www.qstheory.cn</t>
+  </si>
+  <si>
+    <t>光明网</t>
+  </si>
+  <si>
+    <t>http://www.gmw.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>官网,http://www.gmw.cn/</t>
+  </si>
+  <si>
+    <t>中国经济网</t>
+  </si>
+  <si>
+    <t>官网,http://www.ce.cn</t>
+  </si>
+  <si>
+    <t>中国新闻网</t>
+  </si>
+  <si>
+    <t>中新社</t>
+  </si>
+  <si>
+    <t>官网,http://www.chinanews.com</t>
+  </si>
+  <si>
+    <t>法制网</t>
+  </si>
+  <si>
+    <t>法制日报</t>
+  </si>
+  <si>
+    <t>官网,http://www.legaldaily.com.cn/</t>
+  </si>
+  <si>
+    <t>中国农网</t>
+  </si>
+  <si>
+    <t>农民日报</t>
+  </si>
+  <si>
+    <t>官网,http://www.farmer.com.cn/</t>
+  </si>
+  <si>
+    <t>中国妇女网</t>
+  </si>
+  <si>
+    <t>中国妇女报</t>
+  </si>
+  <si>
+    <t>官网,http://www.cnwomen.com.cn/</t>
+  </si>
+  <si>
+    <t>中青在线</t>
+  </si>
+  <si>
+    <t>中国青年报</t>
+  </si>
+  <si>
+    <t>官网,http://www.cyol.com</t>
+  </si>
+  <si>
+    <t>中工网</t>
+  </si>
+  <si>
+    <t>工人日报</t>
+  </si>
+  <si>
+    <t>官网,http://www.workercn.cn</t>
+  </si>
+  <si>
+    <t>中国纪检监察报</t>
+  </si>
+  <si>
+    <t>官网,http://www.jjjcb.cn</t>
+  </si>
+  <si>
+    <t>中国科技网</t>
+  </si>
+  <si>
+    <t>科技日报</t>
+  </si>
+  <si>
+    <t>官网,http://www.stdaily.com</t>
+  </si>
+  <si>
+    <t>央视网</t>
+  </si>
+  <si>
+    <t>https://www.cctv.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>官网,https://www.cctv.com</t>
+  </si>
+  <si>
+    <t>央广网</t>
+  </si>
+  <si>
+    <t>http://www.cnr.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>官网,http://www.cnr.cn/</t>
+  </si>
+  <si>
     <t>常用入口</t>
   </si>
   <si>
@@ -249,12 +399,6 @@
   </si>
   <si>
     <t>官网,https://huggingface.co;模型库,https://huggingface.co/models</t>
-  </si>
-  <si>
-    <t>资讯媒体</t>
-  </si>
-  <si>
-    <t>新华网</t>
   </si>
   <si>
     <t>国家通讯社新华网官方新闻门户</t>
@@ -1411,9 +1555,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1760,7 +1905,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1768,7 +1913,7 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="16.75" customWidth="1"/>
     <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="50.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.125" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.375" customWidth="1"/>
     <col min="8" max="8" width="32.125" style="1" customWidth="1"/>
   </cols>
@@ -1824,7 +1969,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -1835,17 +1980,11 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1859,24 +1998,21 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -1885,24 +2021,18 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -1911,24 +2041,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -1937,24 +2064,18 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -1963,1109 +2084,1569 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="F8" s="2"/>
       <c r="G8" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>70</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F14" s="1"/>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
       <c r="C15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>76</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="F15" s="1"/>
       <c r="G15" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>81</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F16" s="1"/>
       <c r="G16" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" t="s">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" t="s">
-        <v>85</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G17" t="s">
-        <v>87</v>
-      </c>
       <c r="H17" s="1" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" t="s">
-        <v>90</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="G18" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>96</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="F19" s="1"/>
       <c r="G19" t="s">
-        <v>97</v>
+        <v>15</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" t="s">
-        <v>100</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>101</v>
+        <v>57</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="G20" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" t="s">
-        <v>106</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>107</v>
+        <v>60</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="G21" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
       <c r="E22" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="G22" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="E23" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="G23" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>124</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="E26" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="G26" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>135</v>
+        <v>63</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="G28" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="E29" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="G29" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="E30" t="s">
-        <v>152</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>153</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="F30" s="1"/>
       <c r="G30" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
-        <v>157</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>158</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="F31" s="1"/>
       <c r="G31" t="s">
-        <v>159</v>
+        <v>111</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="G32" t="s">
-        <v>164</v>
+        <v>116</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>165</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="G33" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>22</v>
       </c>
       <c r="E34" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="G34" t="s">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="E35" t="s">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="G35" t="s">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>181</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="E36" t="s">
-        <v>183</v>
+        <v>133</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>184</v>
+        <v>134</v>
       </c>
       <c r="G36" t="s">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>186</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="s">
-        <v>187</v>
+        <v>137</v>
       </c>
       <c r="E37" t="s">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="G37" t="s">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>191</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>166</v>
+        <v>13</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="E38" t="s">
-        <v>193</v>
+        <v>143</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>194</v>
+        <v>144</v>
       </c>
       <c r="G38" t="s">
-        <v>195</v>
+        <v>145</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>196</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>197</v>
+        <v>13</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>198</v>
+        <v>147</v>
       </c>
       <c r="E39" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>200</v>
+        <v>149</v>
       </c>
       <c r="G39" t="s">
-        <v>201</v>
+        <v>150</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>202</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="E40" t="s">
-        <v>204</v>
+        <v>154</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="G40" t="s">
-        <v>206</v>
+        <v>156</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>207</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>208</v>
+        <v>158</v>
       </c>
       <c r="E41" t="s">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="G41" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>212</v>
+        <v>162</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>213</v>
+        <v>163</v>
       </c>
       <c r="E42" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="G42" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>217</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>218</v>
+        <v>168</v>
       </c>
       <c r="E43" t="s">
-        <v>219</v>
+        <v>169</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="G43" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>222</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B44" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="E44" t="s">
-        <v>224</v>
+        <v>174</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="G44" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>227</v>
+        <v>152</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="E45" t="s">
-        <v>229</v>
+        <v>179</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="G45" t="s">
-        <v>231</v>
+        <v>181</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="E46" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="G46" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>238</v>
+        <v>189</v>
       </c>
       <c r="E47" t="s">
-        <v>239</v>
+        <v>190</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>240</v>
+        <v>191</v>
       </c>
       <c r="G47" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>242</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>243</v>
+        <v>194</v>
       </c>
       <c r="E48" t="s">
-        <v>244</v>
+        <v>195</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>245</v>
+        <v>196</v>
       </c>
       <c r="G48" t="s">
-        <v>246</v>
+        <v>197</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>247</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>248</v>
+        <v>199</v>
       </c>
       <c r="E49" t="s">
-        <v>249</v>
+        <v>200</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="G49" t="s">
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>251</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
+        <v>30</v>
+      </c>
+      <c r="B50" t="s">
+        <v>183</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" t="s">
+        <v>204</v>
+      </c>
+      <c r="E50" t="s">
+        <v>205</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G50" t="s">
+        <v>207</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51">
+        <v>31</v>
+      </c>
+      <c r="B51" t="s">
+        <v>183</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>209</v>
+      </c>
+      <c r="E51" t="s">
+        <v>210</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G51" t="s">
+        <v>212</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52">
+        <v>32</v>
+      </c>
+      <c r="B52" t="s">
+        <v>214</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52" t="s">
+        <v>215</v>
+      </c>
+      <c r="E52" t="s">
+        <v>216</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G52" t="s">
+        <v>218</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53">
+        <v>33</v>
+      </c>
+      <c r="B53" t="s">
+        <v>214</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>220</v>
+      </c>
+      <c r="E53" t="s">
+        <v>221</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G53" t="s">
+        <v>223</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54">
+        <v>34</v>
+      </c>
+      <c r="B54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54" t="s">
+        <v>225</v>
+      </c>
+      <c r="E54" t="s">
+        <v>226</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="G54" t="s">
+        <v>228</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55">
+        <v>35</v>
+      </c>
+      <c r="B55" t="s">
+        <v>214</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55" t="s">
+        <v>230</v>
+      </c>
+      <c r="E55" t="s">
+        <v>231</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G55" t="s">
+        <v>233</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56">
+        <v>36</v>
+      </c>
+      <c r="B56" t="s">
+        <v>214</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56" t="s">
+        <v>235</v>
+      </c>
+      <c r="E56" t="s">
+        <v>236</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G56" t="s">
+        <v>238</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57">
+        <v>37</v>
+      </c>
+      <c r="B57" t="s">
+        <v>214</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57" t="s">
+        <v>240</v>
+      </c>
+      <c r="E57" t="s">
+        <v>241</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G57" t="s">
+        <v>243</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58">
+        <v>38</v>
+      </c>
+      <c r="B58" t="s">
+        <v>245</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
+        <v>246</v>
+      </c>
+      <c r="E58" t="s">
+        <v>247</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G58" t="s">
+        <v>249</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59">
+        <v>39</v>
+      </c>
+      <c r="B59" t="s">
+        <v>245</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59" t="s">
+        <v>251</v>
+      </c>
+      <c r="E59" t="s">
+        <v>252</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G59" t="s">
+        <v>254</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60">
+        <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>245</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60" t="s">
+        <v>256</v>
+      </c>
+      <c r="E60" t="s">
+        <v>257</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G60" t="s">
+        <v>259</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61">
+        <v>41</v>
+      </c>
+      <c r="B61" t="s">
+        <v>245</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>261</v>
+      </c>
+      <c r="E61" t="s">
+        <v>262</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G61" t="s">
+        <v>264</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62">
+        <v>42</v>
+      </c>
+      <c r="B62" t="s">
+        <v>245</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" t="s">
+        <v>266</v>
+      </c>
+      <c r="E62" t="s">
+        <v>267</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G62" t="s">
+        <v>269</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63">
+        <v>43</v>
+      </c>
+      <c r="B63" t="s">
+        <v>245</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63" t="s">
+        <v>271</v>
+      </c>
+      <c r="E63" t="s">
+        <v>272</v>
+      </c>
+      <c r="G63" t="s">
+        <v>273</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64">
+        <v>44</v>
+      </c>
+      <c r="B64" t="s">
+        <v>275</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+      <c r="D64" t="s">
+        <v>276</v>
+      </c>
+      <c r="E64" t="s">
+        <v>277</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G64" t="s">
+        <v>279</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65">
+        <v>45</v>
+      </c>
+      <c r="B65" t="s">
+        <v>275</v>
+      </c>
+      <c r="C65">
+        <v>2</v>
+      </c>
+      <c r="D65" t="s">
+        <v>281</v>
+      </c>
+      <c r="E65" t="s">
+        <v>282</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G65" t="s">
+        <v>284</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66">
+        <v>46</v>
+      </c>
+      <c r="B66" t="s">
+        <v>275</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+      <c r="D66" t="s">
+        <v>286</v>
+      </c>
+      <c r="E66" t="s">
+        <v>287</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G66" t="s">
+        <v>289</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67">
+        <v>47</v>
+      </c>
+      <c r="B67" t="s">
+        <v>275</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="D67" t="s">
+        <v>291</v>
+      </c>
+      <c r="E67" t="s">
+        <v>292</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G67" t="s">
+        <v>294</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68">
         <v>48</v>
       </c>
-      <c r="B50" t="s">
-        <v>227</v>
-      </c>
-      <c r="C50">
-        <v>2</v>
-      </c>
-      <c r="D50" t="s">
-        <v>252</v>
-      </c>
-      <c r="E50" t="s">
-        <v>253</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="G50" t="s">
-        <v>250</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>255</v>
+      <c r="B68" t="s">
+        <v>275</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+      <c r="D68" t="s">
+        <v>296</v>
+      </c>
+      <c r="E68" t="s">
+        <v>297</v>
+      </c>
+      <c r="F68" s="1"/>
+      <c r="G68" t="s">
+        <v>298</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69">
+        <v>49</v>
+      </c>
+      <c r="B69" t="s">
+        <v>275</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+      <c r="D69" t="s">
+        <v>300</v>
+      </c>
+      <c r="E69" t="s">
+        <v>301</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G69" t="s">
+        <v>298</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H50" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H69" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:H69">
+      <sortCondition ref="A1"/>
+    </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" display="中国政协网,http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="H3" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>
+    <hyperlink ref="H22" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>
     <hyperlink ref="F2" r:id="rId3" display="http://www.cppcc.gov.cn/images/favicon.ico"/>
+    <hyperlink ref="F4" r:id="rId4" display="http://www.chinadaily.com.cn/favicon.ico"/>
+    <hyperlink ref="F6" r:id="rId4" display="http://www.chinadaily.com.cn/favicon.ico"/>
+    <hyperlink ref="F10" r:id="rId5" display="http://www.gmw.cn/favicon.ico"/>
+    <hyperlink ref="F20" r:id="rId6" display="https://www.cctv.com/favicon.ico"/>
+    <hyperlink ref="F21" r:id="rId7" display="http://www.cnr.cn/favicon.ico"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/assets/xlsx/links.xlsx
+++ b/assets/xlsx/links.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18990" windowHeight="11235" tabRatio="400"/>
+    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="400"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
@@ -218,7 +218,7 @@
     <t>http://www.cnr.cn/favicon.ico</t>
   </si>
   <si>
-    <t>官网,http://www.cnr.cn/</t>
+    <t>官网,http://www.cnr.cn/;公众号,http://weixin.qq.com/r/Qhy_pnDE5y2YrTTF90lQ;微博,https://weibo.com/u/1683472727;听中国微博,https://weibo.com/u/1867571077</t>
   </si>
   <si>
     <t>常用入口</t>
@@ -1558,7 +1558,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2222,7 +2222,6 @@
       <c r="E14" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="1"/>
       <c r="G14" t="s">
         <v>15</v>
       </c>
@@ -2246,7 +2245,6 @@
       <c r="E15" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="1"/>
       <c r="G15" t="s">
         <v>15</v>
       </c>
@@ -2270,7 +2268,6 @@
       <c r="E16" t="s">
         <v>47</v>
       </c>
-      <c r="F16" s="1"/>
       <c r="G16" t="s">
         <v>15</v>
       </c>
@@ -2294,7 +2291,6 @@
       <c r="E17" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="1"/>
       <c r="G17" t="s">
         <v>15</v>
       </c>
@@ -2338,7 +2334,6 @@
       <c r="E19" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="1"/>
       <c r="G19" t="s">
         <v>15</v>
       </c>
@@ -2616,7 +2611,6 @@
       <c r="E30" t="s">
         <v>106</v>
       </c>
-      <c r="F30" s="1"/>
       <c r="G30" t="s">
         <v>107</v>
       </c>
@@ -2640,7 +2634,6 @@
       <c r="E31" t="s">
         <v>110</v>
       </c>
-      <c r="F31" s="1"/>
       <c r="G31" t="s">
         <v>111</v>
       </c>
@@ -3597,7 +3590,6 @@
       <c r="E68" t="s">
         <v>297</v>
       </c>
-      <c r="F68" s="1"/>
       <c r="G68" t="s">
         <v>298</v>
       </c>
@@ -3633,7 +3625,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H69" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:H69">
+    <sortState ref="A1:H69">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>

--- a/assets/xlsx/links.xlsx
+++ b/assets/xlsx/links.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="400"/>
+    <workbookView windowWidth="19230" windowHeight="11820" tabRatio="400"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="315">
   <si>
     <t>站序</t>
   </si>
@@ -855,6 +855,39 @@
   </si>
   <si>
     <t>官网,https://www.lanzou.com</t>
+  </si>
+  <si>
+    <t>草料二维码</t>
+  </si>
+  <si>
+    <t>https://static.clewm.net/static/images/favicon.ico</t>
+  </si>
+  <si>
+    <t>二维码生成</t>
+  </si>
+  <si>
+    <t>解码器,https://cli.im/deqr/;首页,https://cli.im/</t>
+  </si>
+  <si>
+    <t>Online QR Scanner</t>
+  </si>
+  <si>
+    <t>https://www.online-qr-scanner.com/favicon/favicon.ico</t>
+  </si>
+  <si>
+    <t>二维码解码</t>
+  </si>
+  <si>
+    <t>解码器,https://www.online-qr-scanner.com/zh/scan-a-qr-code</t>
+  </si>
+  <si>
+    <t>QR Code Scanner</t>
+  </si>
+  <si>
+    <t>https://static.qr-code-scanner.io/favicon/180-1783679024.svg</t>
+  </si>
+  <si>
+    <t>解码器,https://qr-code-scanner.io/zh</t>
   </si>
   <si>
     <t>影音娱乐</t>
@@ -1555,10 +1588,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1905,7 +1939,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1989,7 +2023,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2012,7 +2046,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2032,7 +2066,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2041,21 +2075,18 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2064,18 +2095,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="2"/>
       <c r="G7" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2084,22 +2119,18 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="2"/>
+        <v>27</v>
+      </c>
       <c r="G8" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2108,18 +2139,21 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -2128,21 +2162,18 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2151,18 +2182,21 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -2171,21 +2205,21 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -2194,21 +2228,21 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -2217,21 +2251,21 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -2240,21 +2274,21 @@
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E15" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -2263,21 +2297,21 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -2286,21 +2320,18 @@
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -2309,18 +2340,21 @@
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>54</v>
+      </c>
+      <c r="E18" t="s">
+        <v>55</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -2329,21 +2363,21 @@
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -2352,44 +2386,47 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="E21" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>63</v>
@@ -2398,24 +2435,24 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G22" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>63</v>
@@ -2424,24 +2461,24 @@
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>63</v>
@@ -2450,24 +2487,24 @@
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>63</v>
@@ -2476,24 +2513,24 @@
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E25" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
         <v>63</v>
@@ -2502,50 +2539,50 @@
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G27" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
         <v>94</v>
@@ -2554,24 +2591,24 @@
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
         <v>94</v>
@@ -2580,24 +2617,21 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s">
-        <v>101</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G29" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
         <v>94</v>
@@ -2606,21 +2640,21 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G30" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
         <v>94</v>
@@ -2629,21 +2663,24 @@
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
-        <v>110</v>
+        <v>114</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="G31" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
         <v>94</v>
@@ -2652,50 +2689,50 @@
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E32" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G32" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
         <v>13</v>
       </c>
-      <c r="B33" t="s">
-        <v>94</v>
-      </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="E33" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G33" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -2704,24 +2741,24 @@
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -2730,24 +2767,24 @@
         <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G35" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -2756,24 +2793,24 @@
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E36" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G36" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -2782,24 +2819,24 @@
         <v>2</v>
       </c>
       <c r="D37" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E37" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G37" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -2808,154 +2845,154 @@
         <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E38" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G38" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E39" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G39" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
         <v>152</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E40" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G40" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
         <v>152</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E41" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G41" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
         <v>152</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E42" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G42" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
         <v>152</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E43" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G43" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
         <v>152</v>
@@ -2964,50 +3001,50 @@
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E44" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G44" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E45" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="G45" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
         <v>183</v>
@@ -3016,24 +3053,24 @@
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E46" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G46" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
         <v>183</v>
@@ -3042,24 +3079,24 @@
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E47" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G47" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B48" t="s">
         <v>183</v>
@@ -3068,24 +3105,24 @@
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E48" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G48" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
         <v>183</v>
@@ -3094,24 +3131,24 @@
         <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E49" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G49" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
         <v>183</v>
@@ -3120,50 +3157,50 @@
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E50" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G50" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E51" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G51" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
         <v>214</v>
@@ -3172,24 +3209,24 @@
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E52" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="G52" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B53" t="s">
         <v>214</v>
@@ -3198,50 +3235,50 @@
         <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E53" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="G53" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="B54" t="s">
         <v>214</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E54" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G54" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
         <v>214</v>
@@ -3250,76 +3287,76 @@
         <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E55" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="G55" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B56" t="s">
         <v>214</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E56" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="G56" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E57" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="G57" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B58" t="s">
         <v>245</v>
@@ -3328,24 +3365,24 @@
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E58" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G58" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B59" t="s">
         <v>245</v>
@@ -3354,24 +3391,24 @@
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E59" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="G59" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B60" t="s">
         <v>245</v>
@@ -3380,24 +3417,24 @@
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E60" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="G60" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
         <v>245</v>
@@ -3406,24 +3443,24 @@
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E61" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G61" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B62" t="s">
         <v>245</v>
@@ -3432,24 +3469,21 @@
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E62" t="s">
-        <v>267</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G62" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B63" t="s">
         <v>245</v>
@@ -3458,65 +3492,59 @@
         <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>271</v>
-      </c>
-      <c r="E63" t="s">
-        <v>272</v>
+        <v>275</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="G63" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>276</v>
-      </c>
-      <c r="E64" t="s">
-        <v>277</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>280</v>
       </c>
       <c r="G64" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" t="s">
+        <v>283</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="G65" t="s">
         <v>281</v>
-      </c>
-      <c r="E65" t="s">
-        <v>282</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="G65" t="s">
-        <v>284</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>285</v>
@@ -3524,121 +3552,176 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C66">
         <v>2</v>
       </c>
       <c r="D66" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E66" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G66" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C67">
         <v>2</v>
       </c>
       <c r="D67" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E67" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G67" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C68">
         <v>2</v>
       </c>
       <c r="D68" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E68" t="s">
-        <v>297</v>
+        <v>298</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="G68" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C69">
         <v>2</v>
       </c>
       <c r="D69" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E69" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G69" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>286</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+      <c r="D70" t="s">
+        <v>307</v>
+      </c>
+      <c r="E70" t="s">
+        <v>308</v>
+      </c>
+      <c r="F70" s="1"/>
+      <c r="G70" t="s">
+        <v>309</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>286</v>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+      <c r="D71" t="s">
+        <v>311</v>
+      </c>
+      <c r="E71" t="s">
+        <v>312</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="G71" t="s">
+        <v>309</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H69" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:H69">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H71" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:H71">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" display="中国政协网,http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="H22" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>
+    <hyperlink ref="H21" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>
     <hyperlink ref="F2" r:id="rId3" display="http://www.cppcc.gov.cn/images/favicon.ico"/>
     <hyperlink ref="F4" r:id="rId4" display="http://www.chinadaily.com.cn/favicon.ico"/>
-    <hyperlink ref="F6" r:id="rId4" display="http://www.chinadaily.com.cn/favicon.ico"/>
-    <hyperlink ref="F10" r:id="rId5" display="http://www.gmw.cn/favicon.ico"/>
-    <hyperlink ref="F20" r:id="rId6" display="https://www.cctv.com/favicon.ico"/>
-    <hyperlink ref="F21" r:id="rId7" display="http://www.cnr.cn/favicon.ico"/>
+    <hyperlink ref="F9" r:id="rId5" display="http://www.gmw.cn/favicon.ico"/>
+    <hyperlink ref="F19" r:id="rId6" display="https://www.cctv.com/favicon.ico"/>
+    <hyperlink ref="F20" r:id="rId7" display="http://www.cnr.cn/favicon.ico"/>
+    <hyperlink ref="F65" r:id="rId8" display="https://static.qr-code-scanner.io/favicon/180-1783679024.svg"/>
+    <hyperlink ref="F64" r:id="rId9" display="https://www.online-qr-scanner.com/favicon/favicon.ico"/>
+    <hyperlink ref="F63" r:id="rId10" display="https://static.clewm.net/static/images/favicon.ico"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/assets/xlsx/links.xlsx
+++ b/assets/xlsx/links.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19230" windowHeight="11820" tabRatio="400"/>
+    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="400"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$125</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="437">
   <si>
     <t>站序</t>
   </si>
@@ -69,6 +69,372 @@
   </si>
   <si>
     <t>中国政协网,http://www.cppcc.gov.cn/</t>
+  </si>
+  <si>
+    <t>北京市政协</t>
+  </si>
+  <si>
+    <t>直辖市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.bjzx.gov.cn/ </t>
+  </si>
+  <si>
+    <t>天津市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.tjszx.gov.cn/</t>
+  </si>
+  <si>
+    <t>上海市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.shszx.gov.cn/</t>
+  </si>
+  <si>
+    <t>重庆市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.cqzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>广西壮族自治区政协</t>
+  </si>
+  <si>
+    <t>自治区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.gxzx.gov.cn/ </t>
+  </si>
+  <si>
+    <t>内蒙古自治区政协</t>
+  </si>
+  <si>
+    <t>http://www.nmgzx.gov.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>官网,http://www.nmgzx.gov.cn/webpage/homepage/index.html</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.nxzx.gov.cn/  </t>
+  </si>
+  <si>
+    <t>西藏自治区政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.xizangzx.gov.cn</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.xjzx.gov.cn/  </t>
+  </si>
+  <si>
+    <t>安徽省政协</t>
+  </si>
+  <si>
+    <t>省级</t>
+  </si>
+  <si>
+    <t>官网,http://www.ahzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>福建省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.fjzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>甘肃省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.gszx.gov.cn/</t>
+  </si>
+  <si>
+    <t>广东省政协</t>
+  </si>
+  <si>
+    <t>省级,广东</t>
+  </si>
+  <si>
+    <t>官网,http://www.gdzxb.gov.cn/</t>
+  </si>
+  <si>
+    <t>广州市政协</t>
+  </si>
+  <si>
+    <t>https://www.gzzx.gov.cn/images/iconcf134.ico</t>
+  </si>
+  <si>
+    <t>市级,广东</t>
+  </si>
+  <si>
+    <t>官网,https://www.gzzx.gov.cn</t>
+  </si>
+  <si>
+    <t>深圳市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.szzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>珠海市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.zhzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>汕头市政协</t>
+  </si>
+  <si>
+    <t>市级,汕头,广东</t>
+  </si>
+  <si>
+    <t>官网,http://stzx.shantou.gov.cn/</t>
+  </si>
+  <si>
+    <t>金平区政协</t>
+  </si>
+  <si>
+    <t>http://www.jpzx.gov.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>区级,汕头,广东</t>
+  </si>
+  <si>
+    <t>官网,http://www.jpzx.gov.cn/welcome</t>
+  </si>
+  <si>
+    <t>佛山市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.fszx.gov.cn/</t>
+  </si>
+  <si>
+    <t>韶关市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.sgzxb.gov.cn/</t>
+  </si>
+  <si>
+    <t>河源市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.gdhyzx.gov.cn/hyzx/index.html</t>
+  </si>
+  <si>
+    <t>梅州市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.mzzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>惠州市政协</t>
+  </si>
+  <si>
+    <t>官网,http://zx.huizhou.gov.cn/</t>
+  </si>
+  <si>
+    <t>汕尾市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.swzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>东莞市政协</t>
+  </si>
+  <si>
+    <t>官网,http://dgzx.dg.gov.cn/</t>
+  </si>
+  <si>
+    <t>中山市政协</t>
+  </si>
+  <si>
+    <t>官网,http://zszx.zsnews.cn/</t>
+  </si>
+  <si>
+    <t>江门市政协</t>
+  </si>
+  <si>
+    <t>官网,http://zx.jiangmen.cn/</t>
+  </si>
+  <si>
+    <t>阳江市政协</t>
+  </si>
+  <si>
+    <t>官网,https://www.yjszx.gov.cn/default.html</t>
+  </si>
+  <si>
+    <t>湛江市政协</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>官网,http://www.gdzjzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>茂名市政协</t>
+  </si>
+  <si>
+    <t>官网,http://zx.maoming.gov.cn/website/main/jsp/index.jsp</t>
+  </si>
+  <si>
+    <t>肇庆市政协</t>
+  </si>
+  <si>
+    <t>官网,http://zqzx.gov.cn/index.html</t>
+  </si>
+  <si>
+    <t>潮州市政协</t>
+  </si>
+  <si>
+    <t>官网,http://czzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>揭阳市政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.jieyangzhengxie.gov.cn/ </t>
+  </si>
+  <si>
+    <t>云浮市政协</t>
+  </si>
+  <si>
+    <t>官网,http://zx.yunfu.gov.cn/</t>
+  </si>
+  <si>
+    <t>贵州省政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,https://www.gzszx.gov.cn/ </t>
+  </si>
+  <si>
+    <t>海南省政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.hainanzx.gov.cn/default.html </t>
+  </si>
+  <si>
+    <t>河北省政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.hebzx.gov.cn/ </t>
+  </si>
+  <si>
+    <t>河南省政协</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>官网,http://www.hnzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>黑龙江省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.hljzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>哈尔滨市政协</t>
+  </si>
+  <si>
+    <t>市级</t>
+  </si>
+  <si>
+    <t>官网,https://www.hrbzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>湖北省政协</t>
+  </si>
+  <si>
+    <t>https://www.hbzx.gov.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>官网,https://www.hbzx.gov.cn</t>
+  </si>
+  <si>
+    <t>武汉市政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.whzx.org.cn/  </t>
+  </si>
+  <si>
+    <t>湖南省政协</t>
+  </si>
+  <si>
+    <t>官网,https://www.hunanzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>吉林省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.jlzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>江苏省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.jszx.gov.cn/</t>
+  </si>
+  <si>
+    <t>江西省政协</t>
+  </si>
+  <si>
+    <t>官网,https://jxzx.jxnews.com.cn/</t>
+  </si>
+  <si>
+    <t>辽宁省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.lnzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>青海省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.qhszx.gov.cn/</t>
+  </si>
+  <si>
+    <t>山东省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.sdzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>山西省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.shanxizx.gov.cn/</t>
+  </si>
+  <si>
+    <t>陕西省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.sxzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>四川省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.sczx.gov.cn/</t>
+  </si>
+  <si>
+    <t>云南省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.ynzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>浙江省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.zjzx.gov.cn/</t>
   </si>
   <si>
     <t>资讯媒体</t>
@@ -1588,11 +1954,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1939,14 +2306,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="1" max="1" width="3.875" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="7.875" customWidth="1"/>
     <col min="4" max="4" width="16.75" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="5" max="5" width="8.5" customWidth="1"/>
     <col min="6" max="6" width="15.125" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.375" customWidth="1"/>
     <col min="8" max="8" width="32.125" style="1" customWidth="1"/>
@@ -2003,1725 +2370,2835 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3"/>
+      <c r="G3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="G8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
-      </c>
-      <c r="E21" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G21" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G22" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
         <v>63</v>
       </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="G23" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" t="s">
-        <v>80</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="G24" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="G25" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E26" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E27" t="s">
-        <v>96</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="G27" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" t="s">
-        <v>101</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>105</v>
-      </c>
-      <c r="E29" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
-      </c>
-      <c r="E30" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
-      </c>
-      <c r="E31" t="s">
-        <v>114</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>115</v>
+        <v>79</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="G31" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" t="s">
-        <v>119</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="G32" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" t="s">
-        <v>123</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="G33" t="s">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>126</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E34" t="s">
-        <v>128</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="G34" t="s">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>132</v>
-      </c>
-      <c r="E35" t="s">
-        <v>133</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>137</v>
-      </c>
-      <c r="E36" t="s">
-        <v>138</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
-      </c>
-      <c r="E37" t="s">
-        <v>143</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="G37" t="s">
-        <v>145</v>
+        <v>35</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>147</v>
-      </c>
-      <c r="E38" t="s">
-        <v>148</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="G38" t="s">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>153</v>
-      </c>
-      <c r="E39" t="s">
-        <v>154</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>155</v>
+        <v>96</v>
       </c>
       <c r="G39" t="s">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>158</v>
-      </c>
-      <c r="E40" t="s">
-        <v>159</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>160</v>
+        <v>98</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="G40" t="s">
-        <v>161</v>
+        <v>35</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>162</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>163</v>
-      </c>
-      <c r="E41" t="s">
-        <v>164</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>166</v>
+        <v>35</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>167</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>168</v>
-      </c>
-      <c r="E42" t="s">
-        <v>169</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>170</v>
+        <v>103</v>
       </c>
       <c r="G42" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>173</v>
-      </c>
-      <c r="E43" t="s">
-        <v>174</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>175</v>
+        <v>106</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="G43" t="s">
-        <v>176</v>
+        <v>35</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>177</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>178</v>
-      </c>
-      <c r="E44" t="s">
-        <v>179</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="G44" t="s">
-        <v>181</v>
+        <v>104</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>182</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>184</v>
-      </c>
-      <c r="E45" t="s">
-        <v>185</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
       <c r="G45" t="s">
-        <v>187</v>
+        <v>35</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>188</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>189</v>
-      </c>
-      <c r="E46" t="s">
-        <v>190</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>191</v>
+        <v>113</v>
       </c>
       <c r="G46" t="s">
-        <v>192</v>
+        <v>35</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>193</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>194</v>
-      </c>
-      <c r="E47" t="s">
-        <v>195</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="G47" t="s">
-        <v>197</v>
+        <v>35</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>198</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>199</v>
-      </c>
-      <c r="E48" t="s">
-        <v>200</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>201</v>
+        <v>117</v>
       </c>
       <c r="G48" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>203</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>204</v>
-      </c>
-      <c r="E49" t="s">
-        <v>205</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="G49" t="s">
-        <v>207</v>
+        <v>35</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>208</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>209</v>
-      </c>
-      <c r="E50" t="s">
-        <v>210</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>211</v>
+        <v>121</v>
       </c>
       <c r="G50" t="s">
-        <v>212</v>
+        <v>35</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>213</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>214</v>
+        <v>8</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>215</v>
-      </c>
-      <c r="E51" t="s">
-        <v>216</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>217</v>
+        <v>123</v>
       </c>
       <c r="G51" t="s">
-        <v>218</v>
+        <v>35</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>219</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>214</v>
+        <v>8</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>220</v>
-      </c>
-      <c r="E52" t="s">
-        <v>221</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>222</v>
+        <v>125</v>
       </c>
       <c r="G52" t="s">
-        <v>223</v>
+        <v>35</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>224</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>214</v>
+        <v>8</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>225</v>
-      </c>
-      <c r="E53" t="s">
-        <v>226</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>227</v>
+        <v>127</v>
       </c>
       <c r="G53" t="s">
-        <v>228</v>
+        <v>35</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>229</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>214</v>
+        <v>8</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>230</v>
-      </c>
-      <c r="E54" t="s">
-        <v>231</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>232</v>
+        <v>129</v>
       </c>
       <c r="G54" t="s">
-        <v>233</v>
+        <v>35</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>234</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>214</v>
+        <v>8</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>235</v>
-      </c>
-      <c r="E55" t="s">
-        <v>236</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>237</v>
+        <v>131</v>
       </c>
       <c r="G55" t="s">
-        <v>238</v>
+        <v>35</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>239</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>214</v>
+        <v>8</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>240</v>
-      </c>
-      <c r="E56" t="s">
-        <v>241</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>242</v>
+        <v>133</v>
       </c>
       <c r="G56" t="s">
-        <v>243</v>
+        <v>35</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>244</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>246</v>
-      </c>
-      <c r="E57" t="s">
-        <v>247</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>248</v>
+        <v>136</v>
       </c>
       <c r="G57" t="s">
-        <v>249</v>
+        <v>137</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>250</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>251</v>
-      </c>
-      <c r="E58" t="s">
-        <v>252</v>
+        <v>139</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>253</v>
+        <v>140</v>
       </c>
       <c r="G58" t="s">
-        <v>254</v>
+        <v>137</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>256</v>
-      </c>
-      <c r="E59" t="s">
-        <v>257</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>258</v>
+        <v>142</v>
       </c>
       <c r="G59" t="s">
-        <v>259</v>
+        <v>137</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>260</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="B60" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>261</v>
-      </c>
-      <c r="E60" t="s">
-        <v>262</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>263</v>
+        <v>144</v>
       </c>
       <c r="G60" t="s">
-        <v>264</v>
+        <v>137</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>265</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="B61" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>266</v>
+        <v>146</v>
       </c>
       <c r="E61" t="s">
-        <v>267</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>268</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="F61" s="3"/>
       <c r="G61" t="s">
-        <v>269</v>
+        <v>137</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>270</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>271</v>
-      </c>
-      <c r="E62" t="s">
-        <v>272</v>
+        <v>149</v>
       </c>
       <c r="G62" t="s">
-        <v>273</v>
+        <v>137</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>274</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="C63">
         <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>275</v>
+        <v>151</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>276</v>
+        <v>152</v>
       </c>
       <c r="G63" t="s">
-        <v>277</v>
+        <v>137</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>278</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>279</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>280</v>
+        <v>154</v>
       </c>
       <c r="G64" t="s">
-        <v>281</v>
+        <v>137</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>282</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>245</v>
+        <v>135</v>
       </c>
       <c r="C65">
         <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>283</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>284</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="E65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F65" s="1"/>
       <c r="G65" t="s">
-        <v>281</v>
+        <v>137</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>285</v>
+        <v>158</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>287</v>
+        <v>159</v>
       </c>
       <c r="E66" t="s">
-        <v>288</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>289</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="F66" s="1"/>
       <c r="G66" t="s">
-        <v>290</v>
+        <v>137</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>291</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" t="s">
-        <v>292</v>
+        <v>162</v>
       </c>
       <c r="E67" t="s">
-        <v>293</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>294</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="F67" s="1"/>
       <c r="G67" t="s">
-        <v>295</v>
+        <v>137</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>296</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="B68" t="s">
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>297</v>
+        <v>165</v>
       </c>
       <c r="E68" t="s">
-        <v>298</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>299</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="F68" s="1"/>
       <c r="G68" t="s">
-        <v>300</v>
+        <v>137</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>301</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>302</v>
+        <v>168</v>
       </c>
       <c r="E69" t="s">
-        <v>303</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>304</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="F69" s="1"/>
       <c r="G69" t="s">
-        <v>305</v>
+        <v>137</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>306</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="B70" t="s">
-        <v>286</v>
+        <v>135</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>307</v>
+        <v>171</v>
       </c>
       <c r="E70" t="s">
-        <v>308</v>
-      </c>
-      <c r="F70" s="1"/>
+        <v>172</v>
+      </c>
       <c r="G70" t="s">
-        <v>309</v>
+        <v>137</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>310</v>
+        <v>173</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
+        <v>16</v>
+      </c>
+      <c r="B71" t="s">
+        <v>135</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
+        <v>137</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72">
+        <v>17</v>
+      </c>
+      <c r="B72" t="s">
+        <v>135</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72" t="s">
+        <v>176</v>
+      </c>
+      <c r="E72" t="s">
+        <v>177</v>
+      </c>
+      <c r="F72" s="1"/>
+      <c r="G72" t="s">
+        <v>137</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73">
+        <v>18</v>
+      </c>
+      <c r="B73" t="s">
+        <v>135</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73" t="s">
+        <v>179</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G73" t="s">
+        <v>137</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74">
+        <v>19</v>
+      </c>
+      <c r="B74" t="s">
+        <v>135</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74" t="s">
+        <v>182</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G74" t="s">
+        <v>137</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75">
+        <v>20</v>
+      </c>
+      <c r="B75" t="s">
+        <v>185</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75" t="s">
+        <v>186</v>
+      </c>
+      <c r="E75" t="s">
+        <v>187</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G75" t="s">
+        <v>189</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76">
+        <v>21</v>
+      </c>
+      <c r="B76" t="s">
+        <v>185</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76" t="s">
+        <v>191</v>
+      </c>
+      <c r="E76" t="s">
+        <v>192</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G76" t="s">
+        <v>194</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77">
+        <v>22</v>
+      </c>
+      <c r="B77" t="s">
+        <v>185</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77" t="s">
+        <v>196</v>
+      </c>
+      <c r="E77" t="s">
+        <v>197</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G77" t="s">
+        <v>199</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78">
+        <v>23</v>
+      </c>
+      <c r="B78" t="s">
+        <v>185</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78" t="s">
+        <v>201</v>
+      </c>
+      <c r="E78" t="s">
+        <v>202</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G78" t="s">
+        <v>204</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79">
+        <v>24</v>
+      </c>
+      <c r="B79" t="s">
+        <v>185</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79" t="s">
+        <v>206</v>
+      </c>
+      <c r="E79" t="s">
+        <v>207</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G79" t="s">
+        <v>209</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>185</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80" t="s">
+        <v>211</v>
+      </c>
+      <c r="E80" t="s">
+        <v>212</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G80" t="s">
+        <v>214</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81">
+        <v>26</v>
+      </c>
+      <c r="B81" t="s">
+        <v>216</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81" t="s">
+        <v>217</v>
+      </c>
+      <c r="E81" t="s">
+        <v>218</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G81" t="s">
+        <v>220</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82">
+        <v>27</v>
+      </c>
+      <c r="B82" t="s">
+        <v>216</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82" t="s">
+        <v>222</v>
+      </c>
+      <c r="E82" t="s">
+        <v>223</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G82" t="s">
+        <v>225</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83">
+        <v>28</v>
+      </c>
+      <c r="B83" t="s">
+        <v>216</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83" t="s">
+        <v>227</v>
+      </c>
+      <c r="E83" t="s">
+        <v>228</v>
+      </c>
+      <c r="G83" t="s">
+        <v>229</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84">
+        <v>29</v>
+      </c>
+      <c r="B84" t="s">
+        <v>216</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84" t="s">
+        <v>231</v>
+      </c>
+      <c r="E84" t="s">
+        <v>232</v>
+      </c>
+      <c r="G84" t="s">
+        <v>233</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85">
+        <v>30</v>
+      </c>
+      <c r="B85" t="s">
+        <v>216</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85" t="s">
+        <v>235</v>
+      </c>
+      <c r="E85" t="s">
+        <v>236</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G85" t="s">
+        <v>238</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86">
+        <v>31</v>
+      </c>
+      <c r="B86" t="s">
+        <v>216</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86" t="s">
+        <v>240</v>
+      </c>
+      <c r="E86" t="s">
+        <v>241</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G86" t="s">
+        <v>243</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87">
+        <v>32</v>
+      </c>
+      <c r="B87" t="s">
+        <v>135</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87" t="s">
+        <v>144</v>
+      </c>
+      <c r="E87" t="s">
+        <v>245</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G87" t="s">
+        <v>247</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88">
+        <v>33</v>
+      </c>
+      <c r="B88" t="s">
+        <v>135</v>
+      </c>
+      <c r="C88">
+        <v>2</v>
+      </c>
+      <c r="D88" t="s">
+        <v>249</v>
+      </c>
+      <c r="E88" t="s">
+        <v>250</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G88" t="s">
+        <v>252</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89">
+        <v>34</v>
+      </c>
+      <c r="B89" t="s">
+        <v>135</v>
+      </c>
+      <c r="C89">
+        <v>2</v>
+      </c>
+      <c r="D89" t="s">
+        <v>254</v>
+      </c>
+      <c r="E89" t="s">
+        <v>255</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G89" t="s">
+        <v>257</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90">
+        <v>35</v>
+      </c>
+      <c r="B90" t="s">
+        <v>135</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90" t="s">
+        <v>259</v>
+      </c>
+      <c r="E90" t="s">
+        <v>260</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G90" t="s">
+        <v>262</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91">
+        <v>36</v>
+      </c>
+      <c r="B91" t="s">
+        <v>135</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+      <c r="D91" t="s">
+        <v>264</v>
+      </c>
+      <c r="E91" t="s">
+        <v>265</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G91" t="s">
+        <v>267</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92">
+        <v>37</v>
+      </c>
+      <c r="B92" t="s">
+        <v>135</v>
+      </c>
+      <c r="C92">
+        <v>2</v>
+      </c>
+      <c r="D92" t="s">
+        <v>269</v>
+      </c>
+      <c r="E92" t="s">
+        <v>270</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G92" t="s">
+        <v>272</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93">
+        <v>38</v>
+      </c>
+      <c r="B93" t="s">
+        <v>274</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93" t="s">
+        <v>275</v>
+      </c>
+      <c r="E93" t="s">
+        <v>276</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G93" t="s">
+        <v>278</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94">
+        <v>39</v>
+      </c>
+      <c r="B94" t="s">
+        <v>274</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94" t="s">
+        <v>280</v>
+      </c>
+      <c r="E94" t="s">
+        <v>281</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="G94" t="s">
+        <v>283</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95">
+        <v>40</v>
+      </c>
+      <c r="B95" t="s">
+        <v>274</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="D95" t="s">
+        <v>285</v>
+      </c>
+      <c r="E95" t="s">
+        <v>286</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G95" t="s">
+        <v>288</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96">
+        <v>41</v>
+      </c>
+      <c r="B96" t="s">
+        <v>274</v>
+      </c>
+      <c r="C96">
+        <v>3</v>
+      </c>
+      <c r="D96" t="s">
+        <v>290</v>
+      </c>
+      <c r="E96" t="s">
+        <v>291</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G96" t="s">
+        <v>293</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97">
+        <v>42</v>
+      </c>
+      <c r="B97" t="s">
+        <v>274</v>
+      </c>
+      <c r="C97">
+        <v>2</v>
+      </c>
+      <c r="D97" t="s">
+        <v>295</v>
+      </c>
+      <c r="E97" t="s">
+        <v>296</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G97" t="s">
+        <v>298</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98">
+        <v>43</v>
+      </c>
+      <c r="B98" t="s">
+        <v>274</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+      <c r="D98" t="s">
+        <v>300</v>
+      </c>
+      <c r="E98" t="s">
+        <v>301</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G98" t="s">
+        <v>303</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99">
+        <v>44</v>
+      </c>
+      <c r="B99" t="s">
+        <v>305</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99" t="s">
+        <v>306</v>
+      </c>
+      <c r="E99" t="s">
+        <v>307</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G99" t="s">
+        <v>309</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100">
+        <v>45</v>
+      </c>
+      <c r="B100" t="s">
+        <v>305</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100" t="s">
+        <v>311</v>
+      </c>
+      <c r="E100" t="s">
+        <v>312</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="G100" t="s">
+        <v>314</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101">
+        <v>46</v>
+      </c>
+      <c r="B101" t="s">
+        <v>305</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101" t="s">
+        <v>316</v>
+      </c>
+      <c r="E101" t="s">
+        <v>317</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="G101" t="s">
+        <v>319</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102">
+        <v>47</v>
+      </c>
+      <c r="B102" t="s">
+        <v>305</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102" t="s">
+        <v>321</v>
+      </c>
+      <c r="E102" t="s">
+        <v>322</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="G102" t="s">
+        <v>324</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103">
+        <v>48</v>
+      </c>
+      <c r="B103" t="s">
+        <v>305</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103" t="s">
+        <v>326</v>
+      </c>
+      <c r="E103" t="s">
+        <v>327</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G103" t="s">
+        <v>329</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104">
+        <v>49</v>
+      </c>
+      <c r="B104" t="s">
+        <v>305</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104" t="s">
+        <v>331</v>
+      </c>
+      <c r="E104" t="s">
+        <v>332</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G104" t="s">
+        <v>334</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105">
+        <v>50</v>
+      </c>
+      <c r="B105" t="s">
+        <v>336</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="D105" t="s">
+        <v>337</v>
+      </c>
+      <c r="E105" t="s">
+        <v>338</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="G105" t="s">
+        <v>340</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106">
+        <v>51</v>
+      </c>
+      <c r="B106" t="s">
+        <v>336</v>
+      </c>
+      <c r="C106">
+        <v>2</v>
+      </c>
+      <c r="D106" t="s">
+        <v>342</v>
+      </c>
+      <c r="E106" t="s">
+        <v>343</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G106" t="s">
+        <v>345</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107">
+        <v>52</v>
+      </c>
+      <c r="B107" t="s">
+        <v>336</v>
+      </c>
+      <c r="C107">
+        <v>2</v>
+      </c>
+      <c r="D107" t="s">
+        <v>347</v>
+      </c>
+      <c r="E107" t="s">
+        <v>348</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G107" t="s">
+        <v>350</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108">
+        <v>53</v>
+      </c>
+      <c r="B108" t="s">
+        <v>336</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+      <c r="D108" t="s">
+        <v>352</v>
+      </c>
+      <c r="E108" t="s">
+        <v>353</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G108" t="s">
+        <v>355</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109">
+        <v>54</v>
+      </c>
+      <c r="B109" t="s">
+        <v>336</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109" t="s">
+        <v>357</v>
+      </c>
+      <c r="E109" t="s">
+        <v>358</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G109" t="s">
+        <v>360</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110">
+        <v>55</v>
+      </c>
+      <c r="B110" t="s">
+        <v>336</v>
+      </c>
+      <c r="C110">
+        <v>2</v>
+      </c>
+      <c r="D110" t="s">
+        <v>362</v>
+      </c>
+      <c r="E110" t="s">
+        <v>363</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G110" t="s">
+        <v>365</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111">
+        <v>56</v>
+      </c>
+      <c r="B111" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111" t="s">
+        <v>368</v>
+      </c>
+      <c r="E111" t="s">
+        <v>369</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G111" t="s">
+        <v>371</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112">
+        <v>57</v>
+      </c>
+      <c r="B112" t="s">
+        <v>367</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112" t="s">
+        <v>373</v>
+      </c>
+      <c r="E112" t="s">
+        <v>374</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G112" t="s">
+        <v>376</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113">
+        <v>58</v>
+      </c>
+      <c r="B113" t="s">
+        <v>367</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="D113" t="s">
+        <v>378</v>
+      </c>
+      <c r="E113" t="s">
+        <v>379</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G113" t="s">
+        <v>381</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114">
+        <v>59</v>
+      </c>
+      <c r="B114" t="s">
+        <v>367</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="D114" t="s">
+        <v>383</v>
+      </c>
+      <c r="E114" t="s">
+        <v>384</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="G114" t="s">
+        <v>386</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115">
+        <v>60</v>
+      </c>
+      <c r="B115" t="s">
+        <v>367</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+      <c r="D115" t="s">
+        <v>388</v>
+      </c>
+      <c r="E115" t="s">
+        <v>389</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G115" t="s">
+        <v>391</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116">
+        <v>61</v>
+      </c>
+      <c r="B116" t="s">
+        <v>367</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116" t="s">
+        <v>393</v>
+      </c>
+      <c r="E116" t="s">
+        <v>394</v>
+      </c>
+      <c r="G116" t="s">
+        <v>395</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117">
+        <v>62</v>
+      </c>
+      <c r="B117" t="s">
+        <v>367</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+      <c r="D117" t="s">
+        <v>397</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="G117" t="s">
+        <v>399</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118">
+        <v>63</v>
+      </c>
+      <c r="B118" t="s">
+        <v>367</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118" t="s">
+        <v>401</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="G118" t="s">
+        <v>403</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119">
+        <v>64</v>
+      </c>
+      <c r="B119" t="s">
+        <v>367</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+      <c r="D119" t="s">
+        <v>405</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="G119" t="s">
+        <v>403</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120">
+        <v>65</v>
+      </c>
+      <c r="B120" t="s">
+        <v>408</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+      <c r="D120" t="s">
+        <v>409</v>
+      </c>
+      <c r="E120" t="s">
+        <v>410</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="G120" t="s">
+        <v>412</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121">
+        <v>66</v>
+      </c>
+      <c r="B121" t="s">
+        <v>408</v>
+      </c>
+      <c r="C121">
+        <v>2</v>
+      </c>
+      <c r="D121" t="s">
+        <v>414</v>
+      </c>
+      <c r="E121" t="s">
+        <v>415</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="G121" t="s">
+        <v>417</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122">
+        <v>67</v>
+      </c>
+      <c r="B122" t="s">
+        <v>408</v>
+      </c>
+      <c r="C122">
+        <v>2</v>
+      </c>
+      <c r="D122" t="s">
+        <v>419</v>
+      </c>
+      <c r="E122" t="s">
+        <v>420</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="G122" t="s">
+        <v>422</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123">
+        <v>68</v>
+      </c>
+      <c r="B123" t="s">
+        <v>408</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+      <c r="D123" t="s">
+        <v>424</v>
+      </c>
+      <c r="E123" t="s">
+        <v>425</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="G123" t="s">
+        <v>427</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124">
+        <v>69</v>
+      </c>
+      <c r="B124" t="s">
+        <v>408</v>
+      </c>
+      <c r="C124">
+        <v>2</v>
+      </c>
+      <c r="D124" t="s">
+        <v>429</v>
+      </c>
+      <c r="E124" t="s">
+        <v>430</v>
+      </c>
+      <c r="G124" t="s">
+        <v>431</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
-        <v>286</v>
-      </c>
-      <c r="C71">
+      <c r="B125" t="s">
+        <v>408</v>
+      </c>
+      <c r="C125">
         <v>2</v>
       </c>
-      <c r="D71" t="s">
-        <v>311</v>
-      </c>
-      <c r="E71" t="s">
-        <v>312</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G71" t="s">
-        <v>309</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>314</v>
+      <c r="D125" t="s">
+        <v>433</v>
+      </c>
+      <c r="E125" t="s">
+        <v>434</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="G125" t="s">
+        <v>431</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>436</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H71" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:H71">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H125" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:H125">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" display="中国政协网,http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="H21" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>
+    <hyperlink ref="H75" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>
     <hyperlink ref="F2" r:id="rId3" display="http://www.cppcc.gov.cn/images/favicon.ico"/>
-    <hyperlink ref="F4" r:id="rId4" display="http://www.chinadaily.com.cn/favicon.ico"/>
-    <hyperlink ref="F9" r:id="rId5" display="http://www.gmw.cn/favicon.ico"/>
-    <hyperlink ref="F19" r:id="rId6" display="https://www.cctv.com/favicon.ico"/>
-    <hyperlink ref="F20" r:id="rId7" display="http://www.cnr.cn/favicon.ico"/>
-    <hyperlink ref="F65" r:id="rId8" display="https://static.qr-code-scanner.io/favicon/180-1783679024.svg"/>
-    <hyperlink ref="F64" r:id="rId9" display="https://www.online-qr-scanner.com/favicon/favicon.ico"/>
-    <hyperlink ref="F63" r:id="rId10" display="https://static.clewm.net/static/images/favicon.ico"/>
+    <hyperlink ref="F58" r:id="rId4" display="http://www.chinadaily.com.cn/favicon.ico"/>
+    <hyperlink ref="F63" r:id="rId5" display="http://www.gmw.cn/favicon.ico"/>
+    <hyperlink ref="F73" r:id="rId6" display="https://www.cctv.com/favicon.ico"/>
+    <hyperlink ref="F74" r:id="rId7" display="http://www.cnr.cn/favicon.ico"/>
+    <hyperlink ref="F119" r:id="rId8" display="https://static.qr-code-scanner.io/favicon/180-1783679024.svg"/>
+    <hyperlink ref="F118" r:id="rId9" display="https://www.online-qr-scanner.com/favicon/favicon.ico"/>
+    <hyperlink ref="F117" r:id="rId10" display="https://static.clewm.net/static/images/favicon.ico"/>
+    <hyperlink ref="F8" r:id="rId11" display="http://www.nmgzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="F16" r:id="rId12" display="https://www.gzzx.gov.cn/images/iconcf134.ico"/>
+    <hyperlink ref="F20" r:id="rId13" display="http://www.jpzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="F31" r:id="rId14" display="https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/"/>
+    <hyperlink ref="F40" r:id="rId15" display="https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/"/>
+    <hyperlink ref="F43" r:id="rId16" display="https://www.hbzx.gov.cn/favicon.ico"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/assets/xlsx/links.xlsx
+++ b/assets/xlsx/links.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" tabRatio="400"/>
+    <workbookView windowWidth="14580" windowHeight="6090" tabRatio="400"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$127</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="444">
   <si>
     <t>站序</t>
   </si>
@@ -54,6 +54,27 @@
   </si>
   <si>
     <t>links</t>
+  </si>
+  <si>
+    <t>正协</t>
+  </si>
+  <si>
+    <t>正协导航</t>
+  </si>
+  <si>
+    <t>https://zhengxie.com.cn/assets/images/logo.svg</t>
+  </si>
+  <si>
+    <t>正协导航,https://zhengxie.com.cn</t>
+  </si>
+  <si>
+    <t>正协信息</t>
+  </si>
+  <si>
+    <t>https://zhengxie.info/favicon.ico</t>
+  </si>
+  <si>
+    <t>正协信息,https://zhengxie.info</t>
   </si>
   <si>
     <t>政协</t>
@@ -2306,7 +2327,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="3.875" customWidth="1"/>
@@ -2358,14 +2379,11 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" t="s">
         <v>11</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2379,14 +2397,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3"/>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>14</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2394,7 +2411,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2402,11 +2419,14 @@
       <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2414,19 +2434,20 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F5" s="2"/>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2434,19 +2455,19 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2454,19 +2475,19 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2474,22 +2495,19 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2497,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2517,19 +2535,22 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
         <v>30</v>
       </c>
-      <c r="G10" t="s">
-        <v>23</v>
-      </c>
       <c r="H10" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2537,19 +2558,19 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2557,19 +2578,19 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2577,19 +2598,19 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2597,19 +2618,19 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2617,19 +2638,19 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s">
         <v>42</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2637,19 +2658,16 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>47</v>
@@ -2660,7 +2678,7 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2669,10 +2687,10 @@
         <v>48</v>
       </c>
       <c r="G17" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2680,19 +2698,22 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="G18" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2700,19 +2721,19 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G19" t="s">
         <v>53</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2720,19 +2741,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>58</v>
@@ -2743,7 +2761,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2752,10 +2770,10 @@
         <v>59</v>
       </c>
       <c r="G21" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2763,19 +2781,22 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2783,19 +2804,19 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G23" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2803,19 +2824,19 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G24" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2823,19 +2844,19 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G25" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2843,19 +2864,19 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G26" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2863,19 +2884,19 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -2883,19 +2904,19 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2903,19 +2924,19 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2923,19 +2944,19 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -2943,22 +2964,19 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2966,19 +2984,19 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G32" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -2986,19 +3004,22 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="G33" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3006,19 +3027,19 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -3026,19 +3047,19 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G35" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -3046,19 +3067,19 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -3066,19 +3087,19 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G37" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -3086,19 +3107,19 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G38" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -3106,19 +3127,19 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G39" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -3126,22 +3147,19 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -3149,19 +3167,19 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G41" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -3169,19 +3187,22 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>103</v>
+        <v>105</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="G42" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -3189,22 +3210,19 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>106</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G43" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -3212,19 +3230,19 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G44" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -3232,19 +3250,22 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>111</v>
+        <v>113</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="G45" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -3252,19 +3273,19 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G46" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -3272,19 +3293,19 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G47" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -3292,19 +3313,19 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G48" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -3312,19 +3333,19 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G49" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -3332,19 +3353,19 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G50" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -3352,19 +3373,19 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G51" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -3372,19 +3393,19 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G52" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -3392,19 +3413,19 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C53">
         <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G53" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -3412,19 +3433,19 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -3432,19 +3453,19 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G55" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -3452,59 +3473,56 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G56" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G57" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>139</v>
-      </c>
-      <c r="F58" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G58" t="s">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>141</v>
@@ -3512,370 +3530,361 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G59" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60" t="s">
+        <v>146</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G60" t="s">
         <v>144</v>
       </c>
-      <c r="G60" t="s">
-        <v>137</v>
-      </c>
       <c r="H60" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B61" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>146</v>
-      </c>
-      <c r="E61" t="s">
-        <v>147</v>
-      </c>
-      <c r="F61" s="3"/>
+        <v>149</v>
+      </c>
       <c r="G61" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B62" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G62" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C63">
         <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>151</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>152</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="E63" t="s">
+        <v>154</v>
+      </c>
+      <c r="F63" s="4"/>
       <c r="G63" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G64" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C65">
         <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>156</v>
-      </c>
-      <c r="E65" t="s">
-        <v>157</v>
-      </c>
-      <c r="F65" s="1"/>
+        <v>158</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>159</v>
+      </c>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B66" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>159</v>
-      </c>
-      <c r="E66" t="s">
-        <v>160</v>
-      </c>
-      <c r="F66" s="1"/>
+        <v>161</v>
+      </c>
       <c r="G66" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B67" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C67">
         <v>1</v>
       </c>
       <c r="D67" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E67" t="s">
-        <v>163</v>
-      </c>
-      <c r="F67" s="1"/>
+        <v>164</v>
+      </c>
       <c r="G67" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E68" t="s">
-        <v>166</v>
-      </c>
-      <c r="F68" s="1"/>
+        <v>167</v>
+      </c>
       <c r="G68" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C69">
         <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E69" t="s">
-        <v>169</v>
-      </c>
-      <c r="F69" s="1"/>
+        <v>170</v>
+      </c>
       <c r="G69" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B70" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C70">
         <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E70" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G70" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>174</v>
+        <v>175</v>
+      </c>
+      <c r="E71" t="s">
+        <v>176</v>
       </c>
       <c r="G71" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B72" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
       <c r="D72" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E72" t="s">
-        <v>177</v>
-      </c>
-      <c r="F72" s="1"/>
+        <v>179</v>
+      </c>
       <c r="G72" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B73" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C73">
         <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>179</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G73" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C74">
         <v>1</v>
       </c>
       <c r="D74" t="s">
-        <v>182</v>
-      </c>
-      <c r="F74" s="3" t="s">
         <v>183</v>
       </c>
+      <c r="E74" t="s">
+        <v>184</v>
+      </c>
       <c r="G74" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B75" t="s">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -3883,1140 +3892,1140 @@
       <c r="D75" t="s">
         <v>186</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="G75" t="s">
+        <v>144</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="G75" t="s">
-        <v>189</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B76" t="s">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76" t="s">
+        <v>189</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G76" t="s">
+        <v>144</v>
+      </c>
+      <c r="H76" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="E76" t="s">
-        <v>192</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G76" t="s">
-        <v>194</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B77" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77" t="s">
+        <v>193</v>
+      </c>
+      <c r="E77" t="s">
+        <v>194</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G77" t="s">
         <v>196</v>
       </c>
-      <c r="E77" t="s">
+      <c r="H77" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G77" t="s">
-        <v>199</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B78" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78" t="s">
+        <v>198</v>
+      </c>
+      <c r="E78" t="s">
+        <v>199</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G78" t="s">
         <v>201</v>
       </c>
-      <c r="E78" t="s">
+      <c r="H78" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="G78" t="s">
-        <v>204</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B79" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79" t="s">
+        <v>203</v>
+      </c>
+      <c r="E79" t="s">
+        <v>204</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G79" t="s">
         <v>206</v>
       </c>
-      <c r="E79" t="s">
+      <c r="H79" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G79" t="s">
-        <v>209</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B80" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="s">
+        <v>208</v>
+      </c>
+      <c r="E80" t="s">
+        <v>209</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G80" t="s">
         <v>211</v>
       </c>
-      <c r="E80" t="s">
+      <c r="H80" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="G80" t="s">
-        <v>214</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B81" t="s">
+        <v>192</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81" t="s">
+        <v>213</v>
+      </c>
+      <c r="E81" t="s">
+        <v>214</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G81" t="s">
         <v>216</v>
       </c>
-      <c r="C81">
-        <v>1</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="H81" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="E81" t="s">
-        <v>218</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G81" t="s">
-        <v>220</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
       <c r="D82" t="s">
+        <v>218</v>
+      </c>
+      <c r="E82" t="s">
+        <v>219</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G82" t="s">
+        <v>221</v>
+      </c>
+      <c r="H82" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="E82" t="s">
-        <v>223</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G82" t="s">
-        <v>225</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B83" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C83">
         <v>1</v>
       </c>
       <c r="D83" t="s">
+        <v>224</v>
+      </c>
+      <c r="E83" t="s">
+        <v>225</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G83" t="s">
         <v>227</v>
       </c>
-      <c r="E83" t="s">
+      <c r="H83" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="G83" t="s">
-        <v>229</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C84">
         <v>1</v>
       </c>
       <c r="D84" t="s">
+        <v>229</v>
+      </c>
+      <c r="E84" t="s">
+        <v>230</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="E84" t="s">
+      <c r="G84" t="s">
         <v>232</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B85" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
       <c r="D85" t="s">
+        <v>234</v>
+      </c>
+      <c r="E85" t="s">
         <v>235</v>
       </c>
-      <c r="E85" t="s">
+      <c r="G85" t="s">
         <v>236</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="H85" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="G85" t="s">
-        <v>238</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B86" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" t="s">
+        <v>238</v>
+      </c>
+      <c r="E86" t="s">
+        <v>239</v>
+      </c>
+      <c r="G86" t="s">
         <v>240</v>
       </c>
-      <c r="E86" t="s">
+      <c r="H86" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="G86" t="s">
-        <v>243</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B87" t="s">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>144</v>
+        <v>242</v>
       </c>
       <c r="E87" t="s">
+        <v>243</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G87" t="s">
         <v>245</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="H87" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="G87" t="s">
-        <v>247</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B88" t="s">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" t="s">
+        <v>247</v>
+      </c>
+      <c r="E88" t="s">
+        <v>248</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="E88" t="s">
+      <c r="G88" t="s">
         <v>250</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="H88" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="G88" t="s">
-        <v>252</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B89" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C89">
         <v>2</v>
       </c>
       <c r="D89" t="s">
+        <v>151</v>
+      </c>
+      <c r="E89" t="s">
+        <v>252</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G89" t="s">
         <v>254</v>
       </c>
-      <c r="E89" t="s">
+      <c r="H89" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="G89" t="s">
-        <v>257</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90" t="s">
+        <v>256</v>
+      </c>
+      <c r="E90" t="s">
+        <v>257</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G90" t="s">
         <v>259</v>
       </c>
-      <c r="E90" t="s">
+      <c r="H90" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="G90" t="s">
-        <v>262</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B91" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C91">
         <v>2</v>
       </c>
       <c r="D91" t="s">
+        <v>261</v>
+      </c>
+      <c r="E91" t="s">
+        <v>262</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G91" t="s">
         <v>264</v>
       </c>
-      <c r="E91" t="s">
+      <c r="H91" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="G91" t="s">
-        <v>267</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B92" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92" t="s">
+        <v>266</v>
+      </c>
+      <c r="E92" t="s">
+        <v>267</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G92" t="s">
         <v>269</v>
       </c>
-      <c r="E92" t="s">
+      <c r="H92" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="G92" t="s">
-        <v>272</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B93" t="s">
-        <v>274</v>
+        <v>142</v>
       </c>
       <c r="C93">
         <v>2</v>
       </c>
       <c r="D93" t="s">
+        <v>271</v>
+      </c>
+      <c r="E93" t="s">
+        <v>272</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G93" t="s">
+        <v>274</v>
+      </c>
+      <c r="H93" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="E93" t="s">
-        <v>276</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="G93" t="s">
-        <v>278</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B94" t="s">
-        <v>274</v>
+        <v>142</v>
       </c>
       <c r="C94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" t="s">
+        <v>276</v>
+      </c>
+      <c r="E94" t="s">
+        <v>277</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G94" t="s">
+        <v>279</v>
+      </c>
+      <c r="H94" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="E94" t="s">
-        <v>281</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G94" t="s">
-        <v>283</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B95" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" t="s">
+        <v>282</v>
+      </c>
+      <c r="E95" t="s">
+        <v>283</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="G95" t="s">
         <v>285</v>
       </c>
-      <c r="E95" t="s">
+      <c r="H95" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="G95" t="s">
-        <v>288</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B96" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C96">
         <v>3</v>
       </c>
       <c r="D96" t="s">
+        <v>287</v>
+      </c>
+      <c r="E96" t="s">
+        <v>288</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G96" t="s">
         <v>290</v>
       </c>
-      <c r="E96" t="s">
+      <c r="H96" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="G96" t="s">
-        <v>293</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B97" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" t="s">
+        <v>292</v>
+      </c>
+      <c r="E97" t="s">
+        <v>293</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G97" t="s">
         <v>295</v>
       </c>
-      <c r="E97" t="s">
+      <c r="H97" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="G97" t="s">
-        <v>298</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B98" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D98" t="s">
+        <v>297</v>
+      </c>
+      <c r="E98" t="s">
+        <v>298</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G98" t="s">
         <v>300</v>
       </c>
-      <c r="E98" t="s">
+      <c r="H98" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="G98" t="s">
-        <v>303</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B99" t="s">
+        <v>281</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99" t="s">
+        <v>302</v>
+      </c>
+      <c r="E99" t="s">
+        <v>303</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G99" t="s">
         <v>305</v>
       </c>
-      <c r="C99">
-        <v>1</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="H99" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="E99" t="s">
-        <v>307</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="G99" t="s">
-        <v>309</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B100" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" t="s">
+        <v>307</v>
+      </c>
+      <c r="E100" t="s">
+        <v>308</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="G100" t="s">
+        <v>310</v>
+      </c>
+      <c r="H100" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="E100" t="s">
-        <v>312</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G100" t="s">
-        <v>314</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B101" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C101">
         <v>1</v>
       </c>
       <c r="D101" t="s">
+        <v>313</v>
+      </c>
+      <c r="E101" t="s">
+        <v>314</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G101" t="s">
         <v>316</v>
       </c>
-      <c r="E101" t="s">
+      <c r="H101" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="G101" t="s">
-        <v>319</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B102" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C102">
         <v>1</v>
       </c>
       <c r="D102" t="s">
+        <v>318</v>
+      </c>
+      <c r="E102" t="s">
+        <v>319</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G102" t="s">
         <v>321</v>
       </c>
-      <c r="E102" t="s">
+      <c r="H102" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G102" t="s">
-        <v>324</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B103" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C103">
         <v>1</v>
       </c>
       <c r="D103" t="s">
+        <v>323</v>
+      </c>
+      <c r="E103" t="s">
+        <v>324</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G103" t="s">
         <v>326</v>
       </c>
-      <c r="E103" t="s">
+      <c r="H103" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="G103" t="s">
-        <v>329</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B104" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
       <c r="D104" t="s">
+        <v>328</v>
+      </c>
+      <c r="E104" t="s">
+        <v>329</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G104" t="s">
         <v>331</v>
       </c>
-      <c r="E104" t="s">
+      <c r="H104" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="G104" t="s">
-        <v>334</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B105" t="s">
+        <v>312</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105" t="s">
+        <v>333</v>
+      </c>
+      <c r="E105" t="s">
+        <v>334</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G105" t="s">
         <v>336</v>
       </c>
-      <c r="C105">
-        <v>2</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="H105" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="E105" t="s">
-        <v>338</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="G105" t="s">
-        <v>340</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B106" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" t="s">
+        <v>338</v>
+      </c>
+      <c r="E106" t="s">
+        <v>339</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="G106" t="s">
+        <v>341</v>
+      </c>
+      <c r="H106" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="E106" t="s">
-        <v>343</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="G106" t="s">
-        <v>345</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B107" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C107">
         <v>2</v>
       </c>
       <c r="D107" t="s">
+        <v>344</v>
+      </c>
+      <c r="E107" t="s">
+        <v>345</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G107" t="s">
         <v>347</v>
       </c>
-      <c r="E107" t="s">
+      <c r="H107" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="G107" t="s">
-        <v>350</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B108" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108" t="s">
+        <v>349</v>
+      </c>
+      <c r="E108" t="s">
+        <v>350</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="G108" t="s">
         <v>352</v>
       </c>
-      <c r="E108" t="s">
+      <c r="H108" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="G108" t="s">
-        <v>355</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B109" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" t="s">
+        <v>354</v>
+      </c>
+      <c r="E109" t="s">
+        <v>355</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G109" t="s">
         <v>357</v>
       </c>
-      <c r="E109" t="s">
+      <c r="H109" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="G109" t="s">
-        <v>360</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D110" t="s">
+        <v>359</v>
+      </c>
+      <c r="E110" t="s">
+        <v>360</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G110" t="s">
         <v>362</v>
       </c>
-      <c r="E110" t="s">
+      <c r="H110" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="G110" t="s">
-        <v>365</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B111" t="s">
+        <v>343</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111" t="s">
+        <v>364</v>
+      </c>
+      <c r="E111" t="s">
+        <v>365</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G111" t="s">
         <v>367</v>
       </c>
-      <c r="C111">
-        <v>1</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="H111" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="E111" t="s">
-        <v>369</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G111" t="s">
-        <v>371</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B112" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112" t="s">
+        <v>369</v>
+      </c>
+      <c r="E112" t="s">
+        <v>370</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G112" t="s">
+        <v>372</v>
+      </c>
+      <c r="H112" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="E112" t="s">
-        <v>374</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="G112" t="s">
-        <v>376</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B113" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C113">
         <v>1</v>
       </c>
       <c r="D113" t="s">
+        <v>375</v>
+      </c>
+      <c r="E113" t="s">
+        <v>376</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G113" t="s">
         <v>378</v>
       </c>
-      <c r="E113" t="s">
+      <c r="H113" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="F113" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="G113" t="s">
-        <v>381</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B114" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C114">
         <v>1</v>
       </c>
       <c r="D114" t="s">
+        <v>380</v>
+      </c>
+      <c r="E114" t="s">
+        <v>381</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G114" t="s">
         <v>383</v>
       </c>
-      <c r="E114" t="s">
+      <c r="H114" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="G114" t="s">
-        <v>386</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B115" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C115">
         <v>1</v>
       </c>
       <c r="D115" t="s">
+        <v>385</v>
+      </c>
+      <c r="E115" t="s">
+        <v>386</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="G115" t="s">
         <v>388</v>
       </c>
-      <c r="E115" t="s">
+      <c r="H115" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="G115" t="s">
-        <v>391</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B116" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C116">
         <v>1</v>
       </c>
       <c r="D116" t="s">
+        <v>390</v>
+      </c>
+      <c r="E116" t="s">
+        <v>391</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="G116" t="s">
         <v>393</v>
       </c>
-      <c r="E116" t="s">
+      <c r="H116" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="G116" t="s">
-        <v>395</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B117" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C117">
         <v>1</v>
       </c>
       <c r="D117" t="s">
+        <v>395</v>
+      </c>
+      <c r="E117" t="s">
+        <v>396</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="F117" s="4" t="s">
+      <c r="G117" t="s">
         <v>398</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B118" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C118">
         <v>1</v>
       </c>
       <c r="D118" t="s">
+        <v>400</v>
+      </c>
+      <c r="E118" t="s">
         <v>401</v>
       </c>
-      <c r="F118" s="4" t="s">
+      <c r="G118" t="s">
         <v>402</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B119" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C119">
         <v>1</v>
       </c>
       <c r="D119" t="s">
+        <v>404</v>
+      </c>
+      <c r="F119" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="F119" s="4" t="s">
+      <c r="G119" t="s">
         <v>406</v>
-      </c>
-      <c r="G119" t="s">
-        <v>403</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>407</v>
@@ -5024,181 +5033,229 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B120" t="s">
+        <v>374</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120" t="s">
         <v>408</v>
       </c>
-      <c r="C120">
-        <v>2</v>
-      </c>
-      <c r="D120" t="s">
+      <c r="F120" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="E120" t="s">
+      <c r="G120" t="s">
         <v>410</v>
       </c>
-      <c r="F120" s="1" t="s">
+      <c r="H120" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="G120" t="s">
-        <v>412</v>
-      </c>
-      <c r="H120" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B121" t="s">
-        <v>408</v>
+        <v>374</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121" t="s">
+        <v>412</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="G121" t="s">
+        <v>410</v>
+      </c>
+      <c r="H121" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="E121" t="s">
-        <v>415</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="G121" t="s">
-        <v>417</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B122" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C122">
         <v>2</v>
       </c>
       <c r="D122" t="s">
+        <v>416</v>
+      </c>
+      <c r="E122" t="s">
+        <v>417</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G122" t="s">
         <v>419</v>
       </c>
-      <c r="E122" t="s">
+      <c r="H122" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="G122" t="s">
-        <v>422</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B123" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
+        <v>421</v>
+      </c>
+      <c r="E123" t="s">
+        <v>422</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="G123" t="s">
         <v>424</v>
       </c>
-      <c r="E123" t="s">
+      <c r="H123" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="G123" t="s">
-        <v>427</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B124" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C124">
         <v>2</v>
       </c>
       <c r="D124" t="s">
+        <v>426</v>
+      </c>
+      <c r="E124" t="s">
+        <v>427</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="G124" t="s">
         <v>429</v>
       </c>
-      <c r="E124" t="s">
+      <c r="H124" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="G124" t="s">
-        <v>431</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B125" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
+        <v>431</v>
+      </c>
+      <c r="E125" t="s">
+        <v>432</v>
+      </c>
+      <c r="F125" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="E125" t="s">
+      <c r="G125" t="s">
         <v>434</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="H125" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="G125" t="s">
-        <v>431</v>
-      </c>
-      <c r="H125" s="1" t="s">
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126">
+        <v>69</v>
+      </c>
+      <c r="B126" t="s">
+        <v>415</v>
+      </c>
+      <c r="C126">
+        <v>2</v>
+      </c>
+      <c r="D126" t="s">
         <v>436</v>
       </c>
+      <c r="E126" t="s">
+        <v>437</v>
+      </c>
+      <c r="G126" t="s">
+        <v>438</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127">
+        <v>70</v>
+      </c>
+      <c r="B127" t="s">
+        <v>415</v>
+      </c>
+      <c r="C127">
+        <v>2</v>
+      </c>
+      <c r="D127" t="s">
+        <v>440</v>
+      </c>
+      <c r="E127" t="s">
+        <v>441</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G127" t="s">
+        <v>438</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>443</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H125" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:H125">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H127" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:H127">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" display="中国政协网,http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="H75" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>
-    <hyperlink ref="F2" r:id="rId3" display="http://www.cppcc.gov.cn/images/favicon.ico"/>
-    <hyperlink ref="F58" r:id="rId4" display="http://www.chinadaily.com.cn/favicon.ico"/>
-    <hyperlink ref="F63" r:id="rId5" display="http://www.gmw.cn/favicon.ico"/>
-    <hyperlink ref="F73" r:id="rId6" display="https://www.cctv.com/favicon.ico"/>
-    <hyperlink ref="F74" r:id="rId7" display="http://www.cnr.cn/favicon.ico"/>
-    <hyperlink ref="F119" r:id="rId8" display="https://static.qr-code-scanner.io/favicon/180-1783679024.svg"/>
-    <hyperlink ref="F118" r:id="rId9" display="https://www.online-qr-scanner.com/favicon/favicon.ico"/>
-    <hyperlink ref="F117" r:id="rId10" display="https://static.clewm.net/static/images/favicon.ico"/>
-    <hyperlink ref="F8" r:id="rId11" display="http://www.nmgzx.gov.cn/favicon.ico"/>
-    <hyperlink ref="F16" r:id="rId12" display="https://www.gzzx.gov.cn/images/iconcf134.ico"/>
-    <hyperlink ref="F20" r:id="rId13" display="http://www.jpzx.gov.cn/favicon.ico"/>
-    <hyperlink ref="F31" r:id="rId14" display="https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/"/>
-    <hyperlink ref="F40" r:id="rId15" display="https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/"/>
-    <hyperlink ref="F43" r:id="rId16" display="https://www.hbzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="H4" r:id="rId1" display="中国政协网,http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="H77" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>
+    <hyperlink ref="F4" r:id="rId3" display="http://www.cppcc.gov.cn/images/favicon.ico"/>
+    <hyperlink ref="F60" r:id="rId4" display="http://www.chinadaily.com.cn/favicon.ico"/>
+    <hyperlink ref="F65" r:id="rId5" display="http://www.gmw.cn/favicon.ico"/>
+    <hyperlink ref="F75" r:id="rId6" display="https://www.cctv.com/favicon.ico"/>
+    <hyperlink ref="F76" r:id="rId7" display="http://www.cnr.cn/favicon.ico"/>
+    <hyperlink ref="F121" r:id="rId8" display="https://static.qr-code-scanner.io/favicon/180-1783679024.svg"/>
+    <hyperlink ref="F120" r:id="rId9" display="https://www.online-qr-scanner.com/favicon/favicon.ico"/>
+    <hyperlink ref="F119" r:id="rId10" display="https://static.clewm.net/static/images/favicon.ico"/>
+    <hyperlink ref="F10" r:id="rId11" display="http://www.nmgzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="F18" r:id="rId12" display="https://www.gzzx.gov.cn/images/iconcf134.ico"/>
+    <hyperlink ref="F22" r:id="rId13" display="http://www.jpzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="F33" r:id="rId14" display="https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/"/>
+    <hyperlink ref="F42" r:id="rId15" display="https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/"/>
+    <hyperlink ref="F45" r:id="rId16" display="https://www.hbzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="F3" r:id="rId17" display="https://zhengxie.info/favicon.ico" tooltip="https://zhengxie.info/favicon.ico"/>
+    <hyperlink ref="F2" r:id="rId18" display="https://zhengxie.com.cn/assets/images/logo.svg" tooltip="https://zhengxie.com.cn/assets/images/logo.svg"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/assets/xlsx/links.xlsx
+++ b/assets/xlsx/links.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14580" windowHeight="6090" tabRatio="400"/>
+    <workbookView windowWidth="28800" windowHeight="12300" tabRatio="400"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
@@ -56,6 +56,1293 @@
     <t>links</t>
   </si>
   <si>
+    <t>政协</t>
+  </si>
+  <si>
+    <t>中国人民政治协商会议全国委员会</t>
+  </si>
+  <si>
+    <t>The National Committee of the Chinese People's Political Consultative Conference</t>
+  </si>
+  <si>
+    <t>http://www.cppcc.gov.cn/images/favicon.ico</t>
+  </si>
+  <si>
+    <t>中国政协网,http://www.cppcc.gov.cn/</t>
+  </si>
+  <si>
+    <t>北京市政协</t>
+  </si>
+  <si>
+    <t>直辖市</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.bjzx.gov.cn/ </t>
+  </si>
+  <si>
+    <t>天津市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.tjszx.gov.cn/</t>
+  </si>
+  <si>
+    <t>上海市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.shszx.gov.cn/</t>
+  </si>
+  <si>
+    <t>重庆市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.cqzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>广西壮族自治区政协</t>
+  </si>
+  <si>
+    <t>自治区</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.gxzx.gov.cn/ </t>
+  </si>
+  <si>
+    <t>内蒙古自治区政协</t>
+  </si>
+  <si>
+    <t>http://www.nmgzx.gov.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>官网,http://www.nmgzx.gov.cn/webpage/homepage/index.html</t>
+  </si>
+  <si>
+    <t>宁夏回族自治区政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.nxzx.gov.cn/  </t>
+  </si>
+  <si>
+    <t>西藏自治区政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.xizangzx.gov.cn</t>
+  </si>
+  <si>
+    <t>新疆维吾尔自治区政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.xjzx.gov.cn/  </t>
+  </si>
+  <si>
+    <t>安徽省政协</t>
+  </si>
+  <si>
+    <t>省级</t>
+  </si>
+  <si>
+    <t>官网,http://www.ahzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>福建省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.fjzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>甘肃省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.gszx.gov.cn/</t>
+  </si>
+  <si>
+    <t>广东省政协</t>
+  </si>
+  <si>
+    <t>省级,广东</t>
+  </si>
+  <si>
+    <t>官网,http://www.gdzxb.gov.cn/</t>
+  </si>
+  <si>
+    <t>广州市政协</t>
+  </si>
+  <si>
+    <t>https://www.gzzx.gov.cn/images/iconcf134.ico</t>
+  </si>
+  <si>
+    <t>市级,广东</t>
+  </si>
+  <si>
+    <t>官网,https://www.gzzx.gov.cn</t>
+  </si>
+  <si>
+    <t>深圳市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.szzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>珠海市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.zhzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>汕头市政协</t>
+  </si>
+  <si>
+    <t>市级,汕头,广东</t>
+  </si>
+  <si>
+    <t>官网,http://stzx.shantou.gov.cn/</t>
+  </si>
+  <si>
+    <t>金平区政协</t>
+  </si>
+  <si>
+    <t>http://www.jpzx.gov.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>区级,汕头,广东</t>
+  </si>
+  <si>
+    <t>官网,http://www.jpzx.gov.cn/welcome</t>
+  </si>
+  <si>
+    <t>佛山市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.fszx.gov.cn/</t>
+  </si>
+  <si>
+    <t>韶关市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.sgzxb.gov.cn/</t>
+  </si>
+  <si>
+    <t>河源市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.gdhyzx.gov.cn/hyzx/index.html</t>
+  </si>
+  <si>
+    <t>梅州市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.mzzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>惠州市政协</t>
+  </si>
+  <si>
+    <t>官网,http://zx.huizhou.gov.cn/</t>
+  </si>
+  <si>
+    <t>汕尾市政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.swzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>东莞市政协</t>
+  </si>
+  <si>
+    <t>官网,http://dgzx.dg.gov.cn/</t>
+  </si>
+  <si>
+    <t>中山市政协</t>
+  </si>
+  <si>
+    <t>官网,http://zszx.zsnews.cn/</t>
+  </si>
+  <si>
+    <t>江门市政协</t>
+  </si>
+  <si>
+    <t>官网,http://zx.jiangmen.cn/</t>
+  </si>
+  <si>
+    <t>阳江市政协</t>
+  </si>
+  <si>
+    <t>官网,https://www.yjszx.gov.cn/default.html</t>
+  </si>
+  <si>
+    <t>湛江市政协</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>官网,http://www.gdzjzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>茂名市政协</t>
+  </si>
+  <si>
+    <t>官网,http://zx.maoming.gov.cn/website/main/jsp/index.jsp</t>
+  </si>
+  <si>
+    <t>肇庆市政协</t>
+  </si>
+  <si>
+    <t>官网,http://zqzx.gov.cn/index.html</t>
+  </si>
+  <si>
+    <t>潮州市政协</t>
+  </si>
+  <si>
+    <t>官网,http://czzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>揭阳市政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.jieyangzhengxie.gov.cn/ </t>
+  </si>
+  <si>
+    <t>云浮市政协</t>
+  </si>
+  <si>
+    <t>官网,http://zx.yunfu.gov.cn/</t>
+  </si>
+  <si>
+    <t>贵州省政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,https://www.gzszx.gov.cn/ </t>
+  </si>
+  <si>
+    <t>海南省政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.hainanzx.gov.cn/default.html </t>
+  </si>
+  <si>
+    <t>河北省政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.hebzx.gov.cn/ </t>
+  </si>
+  <si>
+    <t>河南省政协</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>官网,http://www.hnzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>黑龙江省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.hljzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>哈尔滨市政协</t>
+  </si>
+  <si>
+    <t>市级</t>
+  </si>
+  <si>
+    <t>官网,https://www.hrbzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>湖北省政协</t>
+  </si>
+  <si>
+    <t>https://www.hbzx.gov.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>官网,https://www.hbzx.gov.cn</t>
+  </si>
+  <si>
+    <t>武汉市政协</t>
+  </si>
+  <si>
+    <t xml:space="preserve">官网,http://www.whzx.org.cn/  </t>
+  </si>
+  <si>
+    <t>湖南省政协</t>
+  </si>
+  <si>
+    <t>官网,https://www.hunanzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>吉林省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.jlzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>江苏省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.jszx.gov.cn/</t>
+  </si>
+  <si>
+    <t>江西省政协</t>
+  </si>
+  <si>
+    <t>官网,https://jxzx.jxnews.com.cn/</t>
+  </si>
+  <si>
+    <t>辽宁省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.lnzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>青海省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.qhszx.gov.cn/</t>
+  </si>
+  <si>
+    <t>山东省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.sdzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>山西省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.shanxizx.gov.cn/</t>
+  </si>
+  <si>
+    <t>陕西省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.sxzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>四川省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.sczx.gov.cn/</t>
+  </si>
+  <si>
+    <t>云南省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.ynzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>浙江省政协</t>
+  </si>
+  <si>
+    <t>官网,http://www.zjzx.gov.cn/</t>
+  </si>
+  <si>
+    <t>资讯媒体</t>
+  </si>
+  <si>
+    <t>国际在线</t>
+  </si>
+  <si>
+    <t>中央媒体</t>
+  </si>
+  <si>
+    <t>官网,http://www.cri.cn</t>
+  </si>
+  <si>
+    <t>中国日报网</t>
+  </si>
+  <si>
+    <t>http://www.chinadaily.com.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>官网,http://www.chinadaily.com.cn</t>
+  </si>
+  <si>
+    <t>人民网</t>
+  </si>
+  <si>
+    <t>官网,http://www.people.com.cn/</t>
+  </si>
+  <si>
+    <t>新华网</t>
+  </si>
+  <si>
+    <t>官网,http://www.xinhuanet.com</t>
+  </si>
+  <si>
+    <t>中国军网</t>
+  </si>
+  <si>
+    <t>解放军报社</t>
+  </si>
+  <si>
+    <t>官网,http://www.81.cn/</t>
+  </si>
+  <si>
+    <t>求是网</t>
+  </si>
+  <si>
+    <t>官网,http://www.qstheory.cn</t>
+  </si>
+  <si>
+    <t>光明网</t>
+  </si>
+  <si>
+    <t>http://www.gmw.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>官网,http://www.gmw.cn/</t>
+  </si>
+  <si>
+    <t>中国经济网</t>
+  </si>
+  <si>
+    <t>官网,http://www.ce.cn</t>
+  </si>
+  <si>
+    <t>中国新闻网</t>
+  </si>
+  <si>
+    <t>中新社</t>
+  </si>
+  <si>
+    <t>官网,http://www.chinanews.com</t>
+  </si>
+  <si>
+    <t>法制网</t>
+  </si>
+  <si>
+    <t>法制日报</t>
+  </si>
+  <si>
+    <t>官网,http://www.legaldaily.com.cn/</t>
+  </si>
+  <si>
+    <t>中国农网</t>
+  </si>
+  <si>
+    <t>农民日报</t>
+  </si>
+  <si>
+    <t>官网,http://www.farmer.com.cn/</t>
+  </si>
+  <si>
+    <t>中国妇女网</t>
+  </si>
+  <si>
+    <t>中国妇女报</t>
+  </si>
+  <si>
+    <t>官网,http://www.cnwomen.com.cn/</t>
+  </si>
+  <si>
+    <t>中青在线</t>
+  </si>
+  <si>
+    <t>中国青年报</t>
+  </si>
+  <si>
+    <t>官网,http://www.cyol.com</t>
+  </si>
+  <si>
+    <t>中工网</t>
+  </si>
+  <si>
+    <t>工人日报</t>
+  </si>
+  <si>
+    <t>官网,http://www.workercn.cn</t>
+  </si>
+  <si>
+    <t>中国纪检监察报</t>
+  </si>
+  <si>
+    <t>官网,http://www.jjjcb.cn</t>
+  </si>
+  <si>
+    <t>中国科技网</t>
+  </si>
+  <si>
+    <t>科技日报</t>
+  </si>
+  <si>
+    <t>官网,http://www.stdaily.com</t>
+  </si>
+  <si>
+    <t>央视网</t>
+  </si>
+  <si>
+    <t>https://www.cctv.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>官网,https://www.cctv.com</t>
+  </si>
+  <si>
+    <t>央广网</t>
+  </si>
+  <si>
+    <t>http://www.cnr.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>官网,http://www.cnr.cn/;公众号,http://weixin.qq.com/r/Qhy_pnDE5y2YrTTF90lQ;微博,https://weibo.com/u/1683472727;听中国微博,https://weibo.com/u/1867571077</t>
+  </si>
+  <si>
+    <t>常用入口</t>
+  </si>
+  <si>
+    <t>百度</t>
+  </si>
+  <si>
+    <t>全球最大的中文搜索引擎</t>
+  </si>
+  <si>
+    <t>https://www.baidu.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>搜索,中文</t>
+  </si>
+  <si>
+    <t>官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>全球最大搜索引擎与科技公司</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=www.google.com&amp;sz=64</t>
+  </si>
+  <si>
+    <t>搜索,全球</t>
+  </si>
+  <si>
+    <t>官网,https://www.google.com;Gmail,https://mail.google.com;地图,https://www.google.com/maps</t>
+  </si>
+  <si>
+    <t>必应</t>
+  </si>
+  <si>
+    <t>微软出品的智能搜索引擎</t>
+  </si>
+  <si>
+    <t>https://www.bing.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>搜索,微软</t>
+  </si>
+  <si>
+    <t>官网,https://www.bing.com</t>
+  </si>
+  <si>
+    <t>知乎</t>
+  </si>
+  <si>
+    <t>中文互联网高质量问答社区</t>
+  </si>
+  <si>
+    <t>https://www.zhihu.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>问答,社区</t>
+  </si>
+  <si>
+    <t>官网,https://www.zhihu.com;热榜,https://www.zhihu.com/hot;知乎日报,https://daily.zhihu.com</t>
+  </si>
+  <si>
+    <t>豆瓣</t>
+  </si>
+  <si>
+    <t>电影、图书、音乐综合文化社区</t>
+  </si>
+  <si>
+    <t>https://www.douban.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>电影,图书,音乐</t>
+  </si>
+  <si>
+    <t>官网,https://www.douban.com;豆瓣电影,https://movie.douban.com;豆瓣读书,https://book.douban.com</t>
+  </si>
+  <si>
+    <t>微博</t>
+  </si>
+  <si>
+    <t>中文社交媒体与热搜平台</t>
+  </si>
+  <si>
+    <t>https://weibo.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>社交,热搜</t>
+  </si>
+  <si>
+    <t>官网,https://weibo.com;热搜榜,https://s.weibo.com/top/summary</t>
+  </si>
+  <si>
+    <t>AI智能</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
+    <t>OpenAI 打造的对话式 AI 助手</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=chatgpt.com&amp;sz=64</t>
+  </si>
+  <si>
+    <t>对话,GPT</t>
+  </si>
+  <si>
+    <t>官网,https://chatgpt.com;官方文档,https://platform.openai.com</t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>Anthropic 出品的安全对话 AI</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=claude.ai&amp;sz=64</t>
+  </si>
+  <si>
+    <t>对话,写作</t>
+  </si>
+  <si>
+    <t>官网,https://claude.ai;API,https://www.anthropic.com</t>
+  </si>
+  <si>
+    <t>文心一言</t>
+  </si>
+  <si>
+    <t>百度出品的知识增强大语言模型</t>
+  </si>
+  <si>
+    <t>对话,中文</t>
+  </si>
+  <si>
+    <t>官网,https://yiyan.baidu.com</t>
+  </si>
+  <si>
+    <t>Kimi</t>
+  </si>
+  <si>
+    <t>月之暗面出品，擅长长文本阅读</t>
+  </si>
+  <si>
+    <t>对话,长文本</t>
+  </si>
+  <si>
+    <t>官网,https://kimi.moonshot.cn</t>
+  </si>
+  <si>
+    <t>Midjourney</t>
+  </si>
+  <si>
+    <t>顶级 AI 绘画生成平台</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=www.midjourney.com&amp;sz=64</t>
+  </si>
+  <si>
+    <t>绘画,图像</t>
+  </si>
+  <si>
+    <t>官网,https://www.midjourney.com;文档,https://docs.midjourney.com</t>
+  </si>
+  <si>
+    <t>Hugging Face</t>
+  </si>
+  <si>
+    <t>全球最大 AI 模型与数据集社区</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=huggingface.co&amp;sz=64</t>
+  </si>
+  <si>
+    <t>模型,开源</t>
+  </si>
+  <si>
+    <t>官网,https://huggingface.co;模型库,https://huggingface.co/models</t>
+  </si>
+  <si>
+    <t>国家通讯社新华网官方新闻门户</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx13/640/396</t>
+  </si>
+  <si>
+    <t>新闻,时政</t>
+  </si>
+  <si>
+    <t>官网,https://www.news.cn</t>
+  </si>
+  <si>
+    <t>澎湃新闻</t>
+  </si>
+  <si>
+    <t>专注时政与思想的互联网新媒体</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx14/640/396</t>
+  </si>
+  <si>
+    <t>新闻,深度</t>
+  </si>
+  <si>
+    <t>官网,https://www.thepaper.cn</t>
+  </si>
+  <si>
+    <t>36氪</t>
+  </si>
+  <si>
+    <t>中国领先的科技与创投媒体</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx15/640/396</t>
+  </si>
+  <si>
+    <t>科技,创投</t>
+  </si>
+  <si>
+    <t>官网,https://36kr.com</t>
+  </si>
+  <si>
+    <t>虎嗅</t>
+  </si>
+  <si>
+    <t>聚焦科技商业的深度内容平台</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx16/640/396</t>
+  </si>
+  <si>
+    <t>科技,商业</t>
+  </si>
+  <si>
+    <t>官网,https://www.huxiu.com</t>
+  </si>
+  <si>
+    <t>少数派</t>
+  </si>
+  <si>
+    <t>高效工作与数字生活的指南</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx17/640/396</t>
+  </si>
+  <si>
+    <t>数字,生活</t>
+  </si>
+  <si>
+    <t>官网,https://sspai.com</t>
+  </si>
+  <si>
+    <t>爱范儿</t>
+  </si>
+  <si>
+    <t>专注科技与消费的数字媒体</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx18/640/396</t>
+  </si>
+  <si>
+    <t>科技,消费</t>
+  </si>
+  <si>
+    <t>官网,https://www.ifanr.com</t>
+  </si>
+  <si>
+    <t>设计创意</t>
+  </si>
+  <si>
+    <t>站酷</t>
+  </si>
+  <si>
+    <t>中国设计师作品展示与交流平台</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx19/640/396</t>
+  </si>
+  <si>
+    <t>设计,作品</t>
+  </si>
+  <si>
+    <t>官网,https://www.zcool.com.cn</t>
+  </si>
+  <si>
+    <t>花瓣</t>
+  </si>
+  <si>
+    <t>帮你采集与发现灵感的图片社区</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx20/396/640</t>
+  </si>
+  <si>
+    <t>灵感,采集</t>
+  </si>
+  <si>
+    <t>官网,https://huaban.com</t>
+  </si>
+  <si>
+    <t>Dribbble</t>
+  </si>
+  <si>
+    <t>全球设计师作品展示社区</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx21/640/396</t>
+  </si>
+  <si>
+    <t>UI,作品</t>
+  </si>
+  <si>
+    <t>官网,https://dribbble.com</t>
+  </si>
+  <si>
+    <t>Behance</t>
+  </si>
+  <si>
+    <t>Adobe 旗下创意作品展示平台</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx22/396/640</t>
+  </si>
+  <si>
+    <t>作品,创意</t>
+  </si>
+  <si>
+    <t>官网,https://www.behance.net</t>
+  </si>
+  <si>
+    <t>Pinterest</t>
+  </si>
+  <si>
+    <t>图像灵感发现与收藏平台</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx23/640/396</t>
+  </si>
+  <si>
+    <t>灵感,图像</t>
+  </si>
+  <si>
+    <t>官网,https://www.pinterest.com</t>
+  </si>
+  <si>
+    <t>Figma</t>
+  </si>
+  <si>
+    <t>协作式 UI 设计与原型工具</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx24/640/396</t>
+  </si>
+  <si>
+    <t>协作,原型</t>
+  </si>
+  <si>
+    <t>官网,https://www.figma.com</t>
+  </si>
+  <si>
+    <t>开发技术</t>
+  </si>
+  <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>全球最大的代码托管与开源平台</t>
+  </si>
+  <si>
+    <t>https://github.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>代码,开源</t>
+  </si>
+  <si>
+    <t>官网,https://github.com;Trending,https://github.com/trending;排行榜,https://github.com/explore</t>
+  </si>
+  <si>
+    <t>GitLab</t>
+  </si>
+  <si>
+    <t>完整的 DevOps 与 CI/CD 平台</t>
+  </si>
+  <si>
+    <t>https://gitlab.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>代码,CI/CD</t>
+  </si>
+  <si>
+    <t>官网,https://gitlab.com</t>
+  </si>
+  <si>
+    <t>Stack Overflow</t>
+  </si>
+  <si>
+    <t>全球程序员问答社区</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=stackoverflow.com&amp;sz=64</t>
+  </si>
+  <si>
+    <t>问答,编程</t>
+  </si>
+  <si>
+    <t>官网,https://stackoverflow.com</t>
+  </si>
+  <si>
+    <t>MDN</t>
+  </si>
+  <si>
+    <t>Mozilla 权威 Web 开发文档</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=developer.mozilla.org&amp;sz=64</t>
+  </si>
+  <si>
+    <t>文档,前端</t>
+  </si>
+  <si>
+    <t>官网,https://developer.mozilla.org</t>
+  </si>
+  <si>
+    <t>掘金</t>
+  </si>
+  <si>
+    <t>中文技术社区与前端内容平台</t>
+  </si>
+  <si>
+    <t>https://juejin.cn/favicon.ico</t>
+  </si>
+  <si>
+    <t>社区,前端</t>
+  </si>
+  <si>
+    <t>官网,https://juejin.cn</t>
+  </si>
+  <si>
+    <t>V2EX</t>
+  </si>
+  <si>
+    <t>创意工作者们的社区</t>
+  </si>
+  <si>
+    <t>https://www.v2ex.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>社区,极客</t>
+  </si>
+  <si>
+    <t>官网,https://www.v2ex.com</t>
+  </si>
+  <si>
+    <t>学习教育</t>
+  </si>
+  <si>
+    <t>中国大学MOOC</t>
+  </si>
+  <si>
+    <t>国家级精品在线课程平台</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx31/640/396</t>
+  </si>
+  <si>
+    <t>课程,高校</t>
+  </si>
+  <si>
+    <t>官网,https://www.icourse163.org</t>
+  </si>
+  <si>
+    <t>Coursera</t>
+  </si>
+  <si>
+    <t>全球顶尖大学在线课程平台</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx32/640/396</t>
+  </si>
+  <si>
+    <t>课程,国际</t>
+  </si>
+  <si>
+    <t>官网,https://www.coursera.org</t>
+  </si>
+  <si>
+    <t>学堂在线</t>
+  </si>
+  <si>
+    <t>清华大学发起的在线教育平台</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx33/640/396</t>
+  </si>
+  <si>
+    <t>课程,清华</t>
+  </si>
+  <si>
+    <t>官网,https://www.xuetangx.com</t>
+  </si>
+  <si>
+    <t>百度百科</t>
+  </si>
+  <si>
+    <t>人人可编辑的中文百科全书</t>
+  </si>
+  <si>
+    <t>https://baike.baidu.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>百科,查询</t>
+  </si>
+  <si>
+    <t>官网,https://baike.baidu.com</t>
+  </si>
+  <si>
+    <t>维基百科</t>
+  </si>
+  <si>
+    <t>全球开放的协作式百科</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=zh.wikipedia.org&amp;sz=64</t>
+  </si>
+  <si>
+    <t>百科,开放</t>
+  </si>
+  <si>
+    <t>官网,https://zh.wikipedia.org</t>
+  </si>
+  <si>
+    <t>扇贝单词</t>
+  </si>
+  <si>
+    <t>高效背单词的英语学习工具</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx36/640/396</t>
+  </si>
+  <si>
+    <t>英语,背单词</t>
+  </si>
+  <si>
+    <t>官网,https://www.shanbay.com</t>
+  </si>
+  <si>
+    <t>效率工具</t>
+  </si>
+  <si>
+    <t>Notion</t>
+  </si>
+  <si>
+    <t>集笔记、文档、数据库于一体的工作台</t>
+  </si>
+  <si>
+    <t>https://www.google.com/s2/favicons?domain=www.notion.so&amp;sz=64</t>
+  </si>
+  <si>
+    <t>笔记,协作</t>
+  </si>
+  <si>
+    <t>官网,https://www.notion.so;模板,https://www.notion.so/templates</t>
+  </si>
+  <si>
+    <t>印象笔记</t>
+  </si>
+  <si>
+    <t>跨平台笔记与知识管理工具</t>
+  </si>
+  <si>
+    <t>https://www.yinxiang.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>笔记,收藏</t>
+  </si>
+  <si>
+    <t>官网,https://www.yinxiang.com</t>
+  </si>
+  <si>
+    <t>ProcessOn</t>
+  </si>
+  <si>
+    <t>在线思维导图与流程图工具</t>
+  </si>
+  <si>
+    <t>https://www.processon.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>思维导图,流程图</t>
+  </si>
+  <si>
+    <t>官网,https://www.processon.com</t>
+  </si>
+  <si>
+    <t>石墨文档</t>
+  </si>
+  <si>
+    <t>多人实时协作的在线文档</t>
+  </si>
+  <si>
+    <t>https://shimo.im/favicon.ico</t>
+  </si>
+  <si>
+    <t>文档,协作</t>
+  </si>
+  <si>
+    <t>官网,https://shimo.im</t>
+  </si>
+  <si>
+    <t>百度网盘</t>
+  </si>
+  <si>
+    <t>国内主流云存储与分享平台</t>
+  </si>
+  <si>
+    <t>https://pan.baidu.com/favicon.ico</t>
+  </si>
+  <si>
+    <t>网盘,存储</t>
+  </si>
+  <si>
+    <t>官网,https://pan.baidu.com</t>
+  </si>
+  <si>
+    <t>蓝奏云</t>
+  </si>
+  <si>
+    <t>极速上传下载的轻量网盘</t>
+  </si>
+  <si>
+    <t>网盘,分享</t>
+  </si>
+  <si>
+    <t>官网,https://www.lanzou.com</t>
+  </si>
+  <si>
+    <t>草料二维码</t>
+  </si>
+  <si>
+    <t>https://static.clewm.net/static/images/favicon.ico</t>
+  </si>
+  <si>
+    <t>二维码生成</t>
+  </si>
+  <si>
+    <t>解码器,https://cli.im/deqr/;首页,https://cli.im/</t>
+  </si>
+  <si>
+    <t>Online QR Scanner</t>
+  </si>
+  <si>
+    <t>https://www.online-qr-scanner.com/favicon/favicon.ico</t>
+  </si>
+  <si>
+    <t>二维码解码</t>
+  </si>
+  <si>
+    <t>解码器,https://www.online-qr-scanner.com/zh/scan-a-qr-code</t>
+  </si>
+  <si>
+    <t>QR Code Scanner</t>
+  </si>
+  <si>
+    <t>https://static.qr-code-scanner.io/favicon/180-1783679024.svg</t>
+  </si>
+  <si>
+    <t>解码器,https://qr-code-scanner.io/zh</t>
+  </si>
+  <si>
+    <t>影音娱乐</t>
+  </si>
+  <si>
+    <t>哔哩哔哩</t>
+  </si>
+  <si>
+    <t>中国年轻世代高度聚集的视频社区</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx43/640/396</t>
+  </si>
+  <si>
+    <t>视频,弹幕</t>
+  </si>
+  <si>
+    <t>官网,https://www.bilibili.com;排行榜,https://www.bilibili.com/v/popular/rank/all</t>
+  </si>
+  <si>
+    <t>网易云音乐</t>
+  </si>
+  <si>
+    <t>发现好音乐的在线音乐平台</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx44/640/396</t>
+  </si>
+  <si>
+    <t>音乐,歌单</t>
+  </si>
+  <si>
+    <t>官网,https://music.163.com</t>
+  </si>
+  <si>
+    <t>Spotify</t>
+  </si>
+  <si>
+    <t>全球领先的流媒体音乐平台</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx45/640/396</t>
+  </si>
+  <si>
+    <t>音乐,国际</t>
+  </si>
+  <si>
+    <t>官网,https://open.spotify.com</t>
+  </si>
+  <si>
+    <t>YouTube</t>
+  </si>
+  <si>
+    <t>全球最大视频分享平台</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx46/640/396</t>
+  </si>
+  <si>
+    <t>视频,国际</t>
+  </si>
+  <si>
+    <t>官网,https://www.youtube.com</t>
+  </si>
+  <si>
+    <t>爱奇艺</t>
+  </si>
+  <si>
+    <t>在线视频与影视内容平台</t>
+  </si>
+  <si>
+    <t>视频,影视</t>
+  </si>
+  <si>
+    <t>官网,https://www.iqiyi.com</t>
+  </si>
+  <si>
+    <t>腾讯视频</t>
+  </si>
+  <si>
+    <t>腾讯旗下在线视频平台</t>
+  </si>
+  <si>
+    <t>https://picsum.photos/seed/zx48/640/396</t>
+  </si>
+  <si>
+    <t>官网,https://v.qq.com</t>
+  </si>
+  <si>
     <t>正协</t>
   </si>
   <si>
@@ -75,1293 +1362,6 @@
   </si>
   <si>
     <t>正协信息,https://zhengxie.info</t>
-  </si>
-  <si>
-    <t>政协</t>
-  </si>
-  <si>
-    <t>中国人民政治协商会议全国委员会</t>
-  </si>
-  <si>
-    <t>The National Committee of the Chinese People's Political Consultative Conference</t>
-  </si>
-  <si>
-    <t>http://www.cppcc.gov.cn/images/favicon.ico</t>
-  </si>
-  <si>
-    <t>中国政协网,http://www.cppcc.gov.cn/</t>
-  </si>
-  <si>
-    <t>北京市政协</t>
-  </si>
-  <si>
-    <t>直辖市</t>
-  </si>
-  <si>
-    <t xml:space="preserve">官网,http://www.bjzx.gov.cn/ </t>
-  </si>
-  <si>
-    <t>天津市政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.tjszx.gov.cn/</t>
-  </si>
-  <si>
-    <t>上海市政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.shszx.gov.cn/</t>
-  </si>
-  <si>
-    <t>重庆市政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.cqzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>广西壮族自治区政协</t>
-  </si>
-  <si>
-    <t>自治区</t>
-  </si>
-  <si>
-    <t xml:space="preserve">官网,http://www.gxzx.gov.cn/ </t>
-  </si>
-  <si>
-    <t>内蒙古自治区政协</t>
-  </si>
-  <si>
-    <t>http://www.nmgzx.gov.cn/favicon.ico</t>
-  </si>
-  <si>
-    <t>官网,http://www.nmgzx.gov.cn/webpage/homepage/index.html</t>
-  </si>
-  <si>
-    <t>宁夏回族自治区政协</t>
-  </si>
-  <si>
-    <t xml:space="preserve">官网,http://www.nxzx.gov.cn/  </t>
-  </si>
-  <si>
-    <t>西藏自治区政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.xizangzx.gov.cn</t>
-  </si>
-  <si>
-    <t>新疆维吾尔自治区政协</t>
-  </si>
-  <si>
-    <t xml:space="preserve">官网,http://www.xjzx.gov.cn/  </t>
-  </si>
-  <si>
-    <t>安徽省政协</t>
-  </si>
-  <si>
-    <t>省级</t>
-  </si>
-  <si>
-    <t>官网,http://www.ahzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>福建省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.fjzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>甘肃省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.gszx.gov.cn/</t>
-  </si>
-  <si>
-    <t>广东省政协</t>
-  </si>
-  <si>
-    <t>省级,广东</t>
-  </si>
-  <si>
-    <t>官网,http://www.gdzxb.gov.cn/</t>
-  </si>
-  <si>
-    <t>广州市政协</t>
-  </si>
-  <si>
-    <t>https://www.gzzx.gov.cn/images/iconcf134.ico</t>
-  </si>
-  <si>
-    <t>市级,广东</t>
-  </si>
-  <si>
-    <t>官网,https://www.gzzx.gov.cn</t>
-  </si>
-  <si>
-    <t>深圳市政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.szzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>珠海市政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.zhzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>汕头市政协</t>
-  </si>
-  <si>
-    <t>市级,汕头,广东</t>
-  </si>
-  <si>
-    <t>官网,http://stzx.shantou.gov.cn/</t>
-  </si>
-  <si>
-    <t>金平区政协</t>
-  </si>
-  <si>
-    <t>http://www.jpzx.gov.cn/favicon.ico</t>
-  </si>
-  <si>
-    <t>区级,汕头,广东</t>
-  </si>
-  <si>
-    <t>官网,http://www.jpzx.gov.cn/welcome</t>
-  </si>
-  <si>
-    <t>佛山市政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.fszx.gov.cn/</t>
-  </si>
-  <si>
-    <t>韶关市政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.sgzxb.gov.cn/</t>
-  </si>
-  <si>
-    <t>河源市政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.gdhyzx.gov.cn/hyzx/index.html</t>
-  </si>
-  <si>
-    <t>梅州市政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.mzzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>惠州市政协</t>
-  </si>
-  <si>
-    <t>官网,http://zx.huizhou.gov.cn/</t>
-  </si>
-  <si>
-    <t>汕尾市政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.swzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>东莞市政协</t>
-  </si>
-  <si>
-    <t>官网,http://dgzx.dg.gov.cn/</t>
-  </si>
-  <si>
-    <t>中山市政协</t>
-  </si>
-  <si>
-    <t>官网,http://zszx.zsnews.cn/</t>
-  </si>
-  <si>
-    <t>江门市政协</t>
-  </si>
-  <si>
-    <t>官网,http://zx.jiangmen.cn/</t>
-  </si>
-  <si>
-    <t>阳江市政协</t>
-  </si>
-  <si>
-    <t>官网,https://www.yjszx.gov.cn/default.html</t>
-  </si>
-  <si>
-    <t>湛江市政协</t>
-  </si>
-  <si>
-    <t>https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>官网,http://www.gdzjzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>茂名市政协</t>
-  </si>
-  <si>
-    <t>官网,http://zx.maoming.gov.cn/website/main/jsp/index.jsp</t>
-  </si>
-  <si>
-    <t>肇庆市政协</t>
-  </si>
-  <si>
-    <t>官网,http://zqzx.gov.cn/index.html</t>
-  </si>
-  <si>
-    <t>潮州市政协</t>
-  </si>
-  <si>
-    <t>官网,http://czzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>揭阳市政协</t>
-  </si>
-  <si>
-    <t xml:space="preserve">官网,http://www.jieyangzhengxie.gov.cn/ </t>
-  </si>
-  <si>
-    <t>云浮市政协</t>
-  </si>
-  <si>
-    <t>官网,http://zx.yunfu.gov.cn/</t>
-  </si>
-  <si>
-    <t>贵州省政协</t>
-  </si>
-  <si>
-    <t xml:space="preserve">官网,https://www.gzszx.gov.cn/ </t>
-  </si>
-  <si>
-    <t>海南省政协</t>
-  </si>
-  <si>
-    <t xml:space="preserve">官网,http://www.hainanzx.gov.cn/default.html </t>
-  </si>
-  <si>
-    <t>河北省政协</t>
-  </si>
-  <si>
-    <t xml:space="preserve">官网,http://www.hebzx.gov.cn/ </t>
-  </si>
-  <si>
-    <t>河南省政协</t>
-  </si>
-  <si>
-    <t>https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>官网,http://www.hnzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>黑龙江省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.hljzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>哈尔滨市政协</t>
-  </si>
-  <si>
-    <t>市级</t>
-  </si>
-  <si>
-    <t>官网,https://www.hrbzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>湖北省政协</t>
-  </si>
-  <si>
-    <t>https://www.hbzx.gov.cn/favicon.ico</t>
-  </si>
-  <si>
-    <t>官网,https://www.hbzx.gov.cn</t>
-  </si>
-  <si>
-    <t>武汉市政协</t>
-  </si>
-  <si>
-    <t xml:space="preserve">官网,http://www.whzx.org.cn/  </t>
-  </si>
-  <si>
-    <t>湖南省政协</t>
-  </si>
-  <si>
-    <t>官网,https://www.hunanzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>吉林省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.jlzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>江苏省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.jszx.gov.cn/</t>
-  </si>
-  <si>
-    <t>江西省政协</t>
-  </si>
-  <si>
-    <t>官网,https://jxzx.jxnews.com.cn/</t>
-  </si>
-  <si>
-    <t>辽宁省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.lnzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>青海省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.qhszx.gov.cn/</t>
-  </si>
-  <si>
-    <t>山东省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.sdzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>山西省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.shanxizx.gov.cn/</t>
-  </si>
-  <si>
-    <t>陕西省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.sxzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>四川省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.sczx.gov.cn/</t>
-  </si>
-  <si>
-    <t>云南省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.ynzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>浙江省政协</t>
-  </si>
-  <si>
-    <t>官网,http://www.zjzx.gov.cn/</t>
-  </si>
-  <si>
-    <t>资讯媒体</t>
-  </si>
-  <si>
-    <t>国际在线</t>
-  </si>
-  <si>
-    <t>中央媒体</t>
-  </si>
-  <si>
-    <t>官网,http://www.cri.cn</t>
-  </si>
-  <si>
-    <t>中国日报网</t>
-  </si>
-  <si>
-    <t>http://www.chinadaily.com.cn/favicon.ico</t>
-  </si>
-  <si>
-    <t>官网,http://www.chinadaily.com.cn</t>
-  </si>
-  <si>
-    <t>人民网</t>
-  </si>
-  <si>
-    <t>官网,http://www.people.com.cn/</t>
-  </si>
-  <si>
-    <t>新华网</t>
-  </si>
-  <si>
-    <t>官网,http://www.xinhuanet.com</t>
-  </si>
-  <si>
-    <t>中国军网</t>
-  </si>
-  <si>
-    <t>解放军报社</t>
-  </si>
-  <si>
-    <t>官网,http://www.81.cn/</t>
-  </si>
-  <si>
-    <t>求是网</t>
-  </si>
-  <si>
-    <t>官网,http://www.qstheory.cn</t>
-  </si>
-  <si>
-    <t>光明网</t>
-  </si>
-  <si>
-    <t>http://www.gmw.cn/favicon.ico</t>
-  </si>
-  <si>
-    <t>官网,http://www.gmw.cn/</t>
-  </si>
-  <si>
-    <t>中国经济网</t>
-  </si>
-  <si>
-    <t>官网,http://www.ce.cn</t>
-  </si>
-  <si>
-    <t>中国新闻网</t>
-  </si>
-  <si>
-    <t>中新社</t>
-  </si>
-  <si>
-    <t>官网,http://www.chinanews.com</t>
-  </si>
-  <si>
-    <t>法制网</t>
-  </si>
-  <si>
-    <t>法制日报</t>
-  </si>
-  <si>
-    <t>官网,http://www.legaldaily.com.cn/</t>
-  </si>
-  <si>
-    <t>中国农网</t>
-  </si>
-  <si>
-    <t>农民日报</t>
-  </si>
-  <si>
-    <t>官网,http://www.farmer.com.cn/</t>
-  </si>
-  <si>
-    <t>中国妇女网</t>
-  </si>
-  <si>
-    <t>中国妇女报</t>
-  </si>
-  <si>
-    <t>官网,http://www.cnwomen.com.cn/</t>
-  </si>
-  <si>
-    <t>中青在线</t>
-  </si>
-  <si>
-    <t>中国青年报</t>
-  </si>
-  <si>
-    <t>官网,http://www.cyol.com</t>
-  </si>
-  <si>
-    <t>中工网</t>
-  </si>
-  <si>
-    <t>工人日报</t>
-  </si>
-  <si>
-    <t>官网,http://www.workercn.cn</t>
-  </si>
-  <si>
-    <t>中国纪检监察报</t>
-  </si>
-  <si>
-    <t>官网,http://www.jjjcb.cn</t>
-  </si>
-  <si>
-    <t>中国科技网</t>
-  </si>
-  <si>
-    <t>科技日报</t>
-  </si>
-  <si>
-    <t>官网,http://www.stdaily.com</t>
-  </si>
-  <si>
-    <t>央视网</t>
-  </si>
-  <si>
-    <t>https://www.cctv.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>官网,https://www.cctv.com</t>
-  </si>
-  <si>
-    <t>央广网</t>
-  </si>
-  <si>
-    <t>http://www.cnr.cn/favicon.ico</t>
-  </si>
-  <si>
-    <t>官网,http://www.cnr.cn/;公众号,http://weixin.qq.com/r/Qhy_pnDE5y2YrTTF90lQ;微博,https://weibo.com/u/1683472727;听中国微博,https://weibo.com/u/1867571077</t>
-  </si>
-  <si>
-    <t>常用入口</t>
-  </si>
-  <si>
-    <t>百度</t>
-  </si>
-  <si>
-    <t>全球最大的中文搜索引擎</t>
-  </si>
-  <si>
-    <t>https://www.baidu.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>搜索,中文</t>
-  </si>
-  <si>
-    <t>官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>全球最大搜索引擎与科技公司</t>
-  </si>
-  <si>
-    <t>https://www.google.com/s2/favicons?domain=www.google.com&amp;sz=64</t>
-  </si>
-  <si>
-    <t>搜索,全球</t>
-  </si>
-  <si>
-    <t>官网,https://www.google.com;Gmail,https://mail.google.com;地图,https://www.google.com/maps</t>
-  </si>
-  <si>
-    <t>必应</t>
-  </si>
-  <si>
-    <t>微软出品的智能搜索引擎</t>
-  </si>
-  <si>
-    <t>https://www.bing.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>搜索,微软</t>
-  </si>
-  <si>
-    <t>官网,https://www.bing.com</t>
-  </si>
-  <si>
-    <t>知乎</t>
-  </si>
-  <si>
-    <t>中文互联网高质量问答社区</t>
-  </si>
-  <si>
-    <t>https://www.zhihu.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>问答,社区</t>
-  </si>
-  <si>
-    <t>官网,https://www.zhihu.com;热榜,https://www.zhihu.com/hot;知乎日报,https://daily.zhihu.com</t>
-  </si>
-  <si>
-    <t>豆瓣</t>
-  </si>
-  <si>
-    <t>电影、图书、音乐综合文化社区</t>
-  </si>
-  <si>
-    <t>https://www.douban.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>电影,图书,音乐</t>
-  </si>
-  <si>
-    <t>官网,https://www.douban.com;豆瓣电影,https://movie.douban.com;豆瓣读书,https://book.douban.com</t>
-  </si>
-  <si>
-    <t>微博</t>
-  </si>
-  <si>
-    <t>中文社交媒体与热搜平台</t>
-  </si>
-  <si>
-    <t>https://weibo.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>社交,热搜</t>
-  </si>
-  <si>
-    <t>官网,https://weibo.com;热搜榜,https://s.weibo.com/top/summary</t>
-  </si>
-  <si>
-    <t>AI智能</t>
-  </si>
-  <si>
-    <t>ChatGPT</t>
-  </si>
-  <si>
-    <t>OpenAI 打造的对话式 AI 助手</t>
-  </si>
-  <si>
-    <t>https://www.google.com/s2/favicons?domain=chatgpt.com&amp;sz=64</t>
-  </si>
-  <si>
-    <t>对话,GPT</t>
-  </si>
-  <si>
-    <t>官网,https://chatgpt.com;官方文档,https://platform.openai.com</t>
-  </si>
-  <si>
-    <t>Claude</t>
-  </si>
-  <si>
-    <t>Anthropic 出品的安全对话 AI</t>
-  </si>
-  <si>
-    <t>https://www.google.com/s2/favicons?domain=claude.ai&amp;sz=64</t>
-  </si>
-  <si>
-    <t>对话,写作</t>
-  </si>
-  <si>
-    <t>官网,https://claude.ai;API,https://www.anthropic.com</t>
-  </si>
-  <si>
-    <t>文心一言</t>
-  </si>
-  <si>
-    <t>百度出品的知识增强大语言模型</t>
-  </si>
-  <si>
-    <t>对话,中文</t>
-  </si>
-  <si>
-    <t>官网,https://yiyan.baidu.com</t>
-  </si>
-  <si>
-    <t>Kimi</t>
-  </si>
-  <si>
-    <t>月之暗面出品，擅长长文本阅读</t>
-  </si>
-  <si>
-    <t>对话,长文本</t>
-  </si>
-  <si>
-    <t>官网,https://kimi.moonshot.cn</t>
-  </si>
-  <si>
-    <t>Midjourney</t>
-  </si>
-  <si>
-    <t>顶级 AI 绘画生成平台</t>
-  </si>
-  <si>
-    <t>https://www.google.com/s2/favicons?domain=www.midjourney.com&amp;sz=64</t>
-  </si>
-  <si>
-    <t>绘画,图像</t>
-  </si>
-  <si>
-    <t>官网,https://www.midjourney.com;文档,https://docs.midjourney.com</t>
-  </si>
-  <si>
-    <t>Hugging Face</t>
-  </si>
-  <si>
-    <t>全球最大 AI 模型与数据集社区</t>
-  </si>
-  <si>
-    <t>https://www.google.com/s2/favicons?domain=huggingface.co&amp;sz=64</t>
-  </si>
-  <si>
-    <t>模型,开源</t>
-  </si>
-  <si>
-    <t>官网,https://huggingface.co;模型库,https://huggingface.co/models</t>
-  </si>
-  <si>
-    <t>国家通讯社新华网官方新闻门户</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx13/640/396</t>
-  </si>
-  <si>
-    <t>新闻,时政</t>
-  </si>
-  <si>
-    <t>官网,https://www.news.cn</t>
-  </si>
-  <si>
-    <t>澎湃新闻</t>
-  </si>
-  <si>
-    <t>专注时政与思想的互联网新媒体</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx14/640/396</t>
-  </si>
-  <si>
-    <t>新闻,深度</t>
-  </si>
-  <si>
-    <t>官网,https://www.thepaper.cn</t>
-  </si>
-  <si>
-    <t>36氪</t>
-  </si>
-  <si>
-    <t>中国领先的科技与创投媒体</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx15/640/396</t>
-  </si>
-  <si>
-    <t>科技,创投</t>
-  </si>
-  <si>
-    <t>官网,https://36kr.com</t>
-  </si>
-  <si>
-    <t>虎嗅</t>
-  </si>
-  <si>
-    <t>聚焦科技商业的深度内容平台</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx16/640/396</t>
-  </si>
-  <si>
-    <t>科技,商业</t>
-  </si>
-  <si>
-    <t>官网,https://www.huxiu.com</t>
-  </si>
-  <si>
-    <t>少数派</t>
-  </si>
-  <si>
-    <t>高效工作与数字生活的指南</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx17/640/396</t>
-  </si>
-  <si>
-    <t>数字,生活</t>
-  </si>
-  <si>
-    <t>官网,https://sspai.com</t>
-  </si>
-  <si>
-    <t>爱范儿</t>
-  </si>
-  <si>
-    <t>专注科技与消费的数字媒体</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx18/640/396</t>
-  </si>
-  <si>
-    <t>科技,消费</t>
-  </si>
-  <si>
-    <t>官网,https://www.ifanr.com</t>
-  </si>
-  <si>
-    <t>设计创意</t>
-  </si>
-  <si>
-    <t>站酷</t>
-  </si>
-  <si>
-    <t>中国设计师作品展示与交流平台</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx19/640/396</t>
-  </si>
-  <si>
-    <t>设计,作品</t>
-  </si>
-  <si>
-    <t>官网,https://www.zcool.com.cn</t>
-  </si>
-  <si>
-    <t>花瓣</t>
-  </si>
-  <si>
-    <t>帮你采集与发现灵感的图片社区</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx20/396/640</t>
-  </si>
-  <si>
-    <t>灵感,采集</t>
-  </si>
-  <si>
-    <t>官网,https://huaban.com</t>
-  </si>
-  <si>
-    <t>Dribbble</t>
-  </si>
-  <si>
-    <t>全球设计师作品展示社区</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx21/640/396</t>
-  </si>
-  <si>
-    <t>UI,作品</t>
-  </si>
-  <si>
-    <t>官网,https://dribbble.com</t>
-  </si>
-  <si>
-    <t>Behance</t>
-  </si>
-  <si>
-    <t>Adobe 旗下创意作品展示平台</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx22/396/640</t>
-  </si>
-  <si>
-    <t>作品,创意</t>
-  </si>
-  <si>
-    <t>官网,https://www.behance.net</t>
-  </si>
-  <si>
-    <t>Pinterest</t>
-  </si>
-  <si>
-    <t>图像灵感发现与收藏平台</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx23/640/396</t>
-  </si>
-  <si>
-    <t>灵感,图像</t>
-  </si>
-  <si>
-    <t>官网,https://www.pinterest.com</t>
-  </si>
-  <si>
-    <t>Figma</t>
-  </si>
-  <si>
-    <t>协作式 UI 设计与原型工具</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx24/640/396</t>
-  </si>
-  <si>
-    <t>协作,原型</t>
-  </si>
-  <si>
-    <t>官网,https://www.figma.com</t>
-  </si>
-  <si>
-    <t>开发技术</t>
-  </si>
-  <si>
-    <t>GitHub</t>
-  </si>
-  <si>
-    <t>全球最大的代码托管与开源平台</t>
-  </si>
-  <si>
-    <t>https://github.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>代码,开源</t>
-  </si>
-  <si>
-    <t>官网,https://github.com;Trending,https://github.com/trending;排行榜,https://github.com/explore</t>
-  </si>
-  <si>
-    <t>GitLab</t>
-  </si>
-  <si>
-    <t>完整的 DevOps 与 CI/CD 平台</t>
-  </si>
-  <si>
-    <t>https://gitlab.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>代码,CI/CD</t>
-  </si>
-  <si>
-    <t>官网,https://gitlab.com</t>
-  </si>
-  <si>
-    <t>Stack Overflow</t>
-  </si>
-  <si>
-    <t>全球程序员问答社区</t>
-  </si>
-  <si>
-    <t>https://www.google.com/s2/favicons?domain=stackoverflow.com&amp;sz=64</t>
-  </si>
-  <si>
-    <t>问答,编程</t>
-  </si>
-  <si>
-    <t>官网,https://stackoverflow.com</t>
-  </si>
-  <si>
-    <t>MDN</t>
-  </si>
-  <si>
-    <t>Mozilla 权威 Web 开发文档</t>
-  </si>
-  <si>
-    <t>https://www.google.com/s2/favicons?domain=developer.mozilla.org&amp;sz=64</t>
-  </si>
-  <si>
-    <t>文档,前端</t>
-  </si>
-  <si>
-    <t>官网,https://developer.mozilla.org</t>
-  </si>
-  <si>
-    <t>掘金</t>
-  </si>
-  <si>
-    <t>中文技术社区与前端内容平台</t>
-  </si>
-  <si>
-    <t>https://juejin.cn/favicon.ico</t>
-  </si>
-  <si>
-    <t>社区,前端</t>
-  </si>
-  <si>
-    <t>官网,https://juejin.cn</t>
-  </si>
-  <si>
-    <t>V2EX</t>
-  </si>
-  <si>
-    <t>创意工作者们的社区</t>
-  </si>
-  <si>
-    <t>https://www.v2ex.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>社区,极客</t>
-  </si>
-  <si>
-    <t>官网,https://www.v2ex.com</t>
-  </si>
-  <si>
-    <t>学习教育</t>
-  </si>
-  <si>
-    <t>中国大学MOOC</t>
-  </si>
-  <si>
-    <t>国家级精品在线课程平台</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx31/640/396</t>
-  </si>
-  <si>
-    <t>课程,高校</t>
-  </si>
-  <si>
-    <t>官网,https://www.icourse163.org</t>
-  </si>
-  <si>
-    <t>Coursera</t>
-  </si>
-  <si>
-    <t>全球顶尖大学在线课程平台</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx32/640/396</t>
-  </si>
-  <si>
-    <t>课程,国际</t>
-  </si>
-  <si>
-    <t>官网,https://www.coursera.org</t>
-  </si>
-  <si>
-    <t>学堂在线</t>
-  </si>
-  <si>
-    <t>清华大学发起的在线教育平台</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx33/640/396</t>
-  </si>
-  <si>
-    <t>课程,清华</t>
-  </si>
-  <si>
-    <t>官网,https://www.xuetangx.com</t>
-  </si>
-  <si>
-    <t>百度百科</t>
-  </si>
-  <si>
-    <t>人人可编辑的中文百科全书</t>
-  </si>
-  <si>
-    <t>https://baike.baidu.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>百科,查询</t>
-  </si>
-  <si>
-    <t>官网,https://baike.baidu.com</t>
-  </si>
-  <si>
-    <t>维基百科</t>
-  </si>
-  <si>
-    <t>全球开放的协作式百科</t>
-  </si>
-  <si>
-    <t>https://www.google.com/s2/favicons?domain=zh.wikipedia.org&amp;sz=64</t>
-  </si>
-  <si>
-    <t>百科,开放</t>
-  </si>
-  <si>
-    <t>官网,https://zh.wikipedia.org</t>
-  </si>
-  <si>
-    <t>扇贝单词</t>
-  </si>
-  <si>
-    <t>高效背单词的英语学习工具</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx36/640/396</t>
-  </si>
-  <si>
-    <t>英语,背单词</t>
-  </si>
-  <si>
-    <t>官网,https://www.shanbay.com</t>
-  </si>
-  <si>
-    <t>效率工具</t>
-  </si>
-  <si>
-    <t>Notion</t>
-  </si>
-  <si>
-    <t>集笔记、文档、数据库于一体的工作台</t>
-  </si>
-  <si>
-    <t>https://www.google.com/s2/favicons?domain=www.notion.so&amp;sz=64</t>
-  </si>
-  <si>
-    <t>笔记,协作</t>
-  </si>
-  <si>
-    <t>官网,https://www.notion.so;模板,https://www.notion.so/templates</t>
-  </si>
-  <si>
-    <t>印象笔记</t>
-  </si>
-  <si>
-    <t>跨平台笔记与知识管理工具</t>
-  </si>
-  <si>
-    <t>https://www.yinxiang.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>笔记,收藏</t>
-  </si>
-  <si>
-    <t>官网,https://www.yinxiang.com</t>
-  </si>
-  <si>
-    <t>ProcessOn</t>
-  </si>
-  <si>
-    <t>在线思维导图与流程图工具</t>
-  </si>
-  <si>
-    <t>https://www.processon.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>思维导图,流程图</t>
-  </si>
-  <si>
-    <t>官网,https://www.processon.com</t>
-  </si>
-  <si>
-    <t>石墨文档</t>
-  </si>
-  <si>
-    <t>多人实时协作的在线文档</t>
-  </si>
-  <si>
-    <t>https://shimo.im/favicon.ico</t>
-  </si>
-  <si>
-    <t>文档,协作</t>
-  </si>
-  <si>
-    <t>官网,https://shimo.im</t>
-  </si>
-  <si>
-    <t>百度网盘</t>
-  </si>
-  <si>
-    <t>国内主流云存储与分享平台</t>
-  </si>
-  <si>
-    <t>https://pan.baidu.com/favicon.ico</t>
-  </si>
-  <si>
-    <t>网盘,存储</t>
-  </si>
-  <si>
-    <t>官网,https://pan.baidu.com</t>
-  </si>
-  <si>
-    <t>蓝奏云</t>
-  </si>
-  <si>
-    <t>极速上传下载的轻量网盘</t>
-  </si>
-  <si>
-    <t>网盘,分享</t>
-  </si>
-  <si>
-    <t>官网,https://www.lanzou.com</t>
-  </si>
-  <si>
-    <t>草料二维码</t>
-  </si>
-  <si>
-    <t>https://static.clewm.net/static/images/favicon.ico</t>
-  </si>
-  <si>
-    <t>二维码生成</t>
-  </si>
-  <si>
-    <t>解码器,https://cli.im/deqr/;首页,https://cli.im/</t>
-  </si>
-  <si>
-    <t>Online QR Scanner</t>
-  </si>
-  <si>
-    <t>https://www.online-qr-scanner.com/favicon/favicon.ico</t>
-  </si>
-  <si>
-    <t>二维码解码</t>
-  </si>
-  <si>
-    <t>解码器,https://www.online-qr-scanner.com/zh/scan-a-qr-code</t>
-  </si>
-  <si>
-    <t>QR Code Scanner</t>
-  </si>
-  <si>
-    <t>https://static.qr-code-scanner.io/favicon/180-1783679024.svg</t>
-  </si>
-  <si>
-    <t>解码器,https://qr-code-scanner.io/zh</t>
-  </si>
-  <si>
-    <t>影音娱乐</t>
-  </si>
-  <si>
-    <t>哔哩哔哩</t>
-  </si>
-  <si>
-    <t>中国年轻世代高度聚集的视频社区</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx43/640/396</t>
-  </si>
-  <si>
-    <t>视频,弹幕</t>
-  </si>
-  <si>
-    <t>官网,https://www.bilibili.com;排行榜,https://www.bilibili.com/v/popular/rank/all</t>
-  </si>
-  <si>
-    <t>网易云音乐</t>
-  </si>
-  <si>
-    <t>发现好音乐的在线音乐平台</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx44/640/396</t>
-  </si>
-  <si>
-    <t>音乐,歌单</t>
-  </si>
-  <si>
-    <t>官网,https://music.163.com</t>
-  </si>
-  <si>
-    <t>Spotify</t>
-  </si>
-  <si>
-    <t>全球领先的流媒体音乐平台</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx45/640/396</t>
-  </si>
-  <si>
-    <t>音乐,国际</t>
-  </si>
-  <si>
-    <t>官网,https://open.spotify.com</t>
-  </si>
-  <si>
-    <t>YouTube</t>
-  </si>
-  <si>
-    <t>全球最大视频分享平台</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx46/640/396</t>
-  </si>
-  <si>
-    <t>视频,国际</t>
-  </si>
-  <si>
-    <t>官网,https://www.youtube.com</t>
-  </si>
-  <si>
-    <t>爱奇艺</t>
-  </si>
-  <si>
-    <t>在线视频与影视内容平台</t>
-  </si>
-  <si>
-    <t>视频,影视</t>
-  </si>
-  <si>
-    <t>官网,https://www.iqiyi.com</t>
-  </si>
-  <si>
-    <t>腾讯视频</t>
-  </si>
-  <si>
-    <t>腾讯旗下在线视频平台</t>
-  </si>
-  <si>
-    <t>https://picsum.photos/seed/zx48/640/396</t>
-  </si>
-  <si>
-    <t>官网,https://v.qq.com</t>
   </si>
 </sst>
 </file>
@@ -1975,63 +1975,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2330,7 +2328,7 @@
   <dimension ref="A1:H127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="3.875" customWidth="1"/>
+    <col min="1" max="1" width="9.75" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="7.875" customWidth="1"/>
     <col min="4" max="4" width="16.75" customWidth="1"/>
@@ -2368,7 +2366,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -2379,16 +2377,19 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -2397,21 +2398,22 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H3" t="s">
+      <c r="F3" s="2"/>
+      <c r="G3" t="s">
         <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -2419,255 +2421,254 @@
       <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2"/>
+        <v>18</v>
+      </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="G9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
         <v>42</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" t="s">
         <v>46</v>
-      </c>
-      <c r="G16" t="s">
-        <v>42</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>47</v>
@@ -2675,10 +2676,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2687,70 +2688,70 @@
         <v>48</v>
       </c>
       <c r="G17" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G19" t="s">
         <v>53</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" t="s">
         <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>53</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>58</v>
@@ -2758,10 +2759,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2770,759 +2771,759 @@
         <v>59</v>
       </c>
       <c r="G21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G22" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G23" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G24" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G25" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G26" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G27" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G28" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>79</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="G31" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G32" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>86</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G33" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G34" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G37" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G38" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G39" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="G40" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G41" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42" t="s">
+        <v>103</v>
+      </c>
+      <c r="G42" t="s">
+        <v>104</v>
+      </c>
+      <c r="H42" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G42" t="s">
-        <v>42</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
+        <v>106</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G43" t="s">
+        <v>35</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="G43" t="s">
-        <v>42</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44" t="s">
+        <v>109</v>
+      </c>
+      <c r="G44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="G44" t="s">
-        <v>111</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>113</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G45" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G46" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G47" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G48" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="G49" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G50" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G51" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G52" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C53">
         <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G53" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G54" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G55" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G56" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" t="s">
+        <v>136</v>
+      </c>
+      <c r="G57" t="s">
+        <v>137</v>
+      </c>
+      <c r="H57" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="G57" t="s">
-        <v>42</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
+        <v>139</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G58" t="s">
-        <v>42</v>
+        <v>137</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>141</v>
@@ -3530,361 +3531,364 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="B59" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59" t="s">
         <v>142</v>
       </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="G59" t="s">
+        <v>137</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>143</v>
-      </c>
-      <c r="G59" t="s">
-        <v>144</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C60">
         <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>146</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G60" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>149</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="E61" t="s">
+        <v>147</v>
+      </c>
+      <c r="F61" s="2"/>
       <c r="G61" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G62" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C63">
         <v>1</v>
       </c>
       <c r="D63" t="s">
+        <v>151</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G63" t="s">
+        <v>137</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="E63" t="s">
-        <v>154</v>
-      </c>
-      <c r="F63" s="4"/>
-      <c r="G63" t="s">
-        <v>144</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G64" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C65">
         <v>1</v>
       </c>
       <c r="D65" t="s">
+        <v>156</v>
+      </c>
+      <c r="E65" t="s">
+        <v>157</v>
+      </c>
+      <c r="G65" t="s">
+        <v>137</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="G65" t="s">
-        <v>144</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="s">
+        <v>159</v>
+      </c>
+      <c r="E66" t="s">
+        <v>160</v>
+      </c>
+      <c r="G66" t="s">
+        <v>137</v>
+      </c>
+      <c r="H66" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>144</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C67">
         <v>1</v>
       </c>
       <c r="D67" t="s">
+        <v>162</v>
+      </c>
+      <c r="E67" t="s">
         <v>163</v>
       </c>
-      <c r="E67" t="s">
+      <c r="G67" t="s">
+        <v>137</v>
+      </c>
+      <c r="H67" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="G67" t="s">
-        <v>144</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68" t="s">
+        <v>165</v>
+      </c>
+      <c r="E68" t="s">
         <v>166</v>
       </c>
-      <c r="E68" t="s">
+      <c r="G68" t="s">
+        <v>137</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="G68" t="s">
-        <v>144</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C69">
         <v>1</v>
       </c>
       <c r="D69" t="s">
+        <v>168</v>
+      </c>
+      <c r="E69" t="s">
         <v>169</v>
       </c>
-      <c r="E69" t="s">
+      <c r="G69" t="s">
+        <v>137</v>
+      </c>
+      <c r="H69" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="G69" t="s">
-        <v>144</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C70">
         <v>1</v>
       </c>
       <c r="D70" t="s">
+        <v>171</v>
+      </c>
+      <c r="E70" t="s">
         <v>172</v>
       </c>
-      <c r="E70" t="s">
+      <c r="G70" t="s">
+        <v>137</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="G70" t="s">
-        <v>144</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" t="s">
+        <v>137</v>
+      </c>
+      <c r="H71" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="E71" t="s">
-        <v>176</v>
-      </c>
-      <c r="G71" t="s">
-        <v>144</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C72">
         <v>1</v>
       </c>
       <c r="D72" t="s">
+        <v>176</v>
+      </c>
+      <c r="E72" t="s">
+        <v>177</v>
+      </c>
+      <c r="G72" t="s">
+        <v>137</v>
+      </c>
+      <c r="H72" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="E72" t="s">
-        <v>179</v>
-      </c>
-      <c r="G72" t="s">
-        <v>144</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C73">
         <v>1</v>
       </c>
       <c r="D73" t="s">
+        <v>179</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G73" t="s">
+        <v>137</v>
+      </c>
+      <c r="H73" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="G73" t="s">
-        <v>144</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C74">
         <v>1</v>
       </c>
       <c r="D74" t="s">
+        <v>182</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E74" t="s">
+      <c r="G74" t="s">
+        <v>137</v>
+      </c>
+      <c r="H74" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="G74" t="s">
-        <v>144</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -3892,1140 +3896,1140 @@
       <c r="D75" t="s">
         <v>186</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="E75" t="s">
         <v>187</v>
       </c>
+      <c r="F75" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="G75" t="s">
-        <v>144</v>
+        <v>189</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>142</v>
+        <v>185</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>189</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
+      </c>
+      <c r="E76" t="s">
+        <v>192</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="G76" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E77" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G77" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E78" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G78" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E79" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="G79" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E80" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G80" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E81" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G81" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E82" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G82" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C83">
         <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E83" t="s">
-        <v>225</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G83" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C84">
         <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E84" t="s">
-        <v>230</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G84" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="B85" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E85" t="s">
-        <v>235</v>
+        <v>236</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="G85" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="B86" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E86" t="s">
-        <v>239</v>
+        <v>241</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="G86" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="B87" t="s">
-        <v>223</v>
+        <v>135</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>242</v>
+        <v>144</v>
       </c>
       <c r="E87" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G87" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="B88" t="s">
-        <v>223</v>
+        <v>135</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E88" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G88" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C89">
         <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>151</v>
+        <v>254</v>
       </c>
       <c r="E89" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G89" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E90" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G90" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C91">
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E91" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G91" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E92" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G92" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="B93" t="s">
-        <v>142</v>
+        <v>274</v>
       </c>
       <c r="C93">
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E93" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G93" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="B94" t="s">
-        <v>142</v>
+        <v>274</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E94" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G94" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="B95" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E95" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G95" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="B96" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C96">
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E96" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="G96" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E97" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G97" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E98" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G98" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="B99" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E99" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G99" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="B100" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E100" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G100" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>44</v>
+        <v>102</v>
       </c>
       <c r="B101" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C101">
         <v>1</v>
       </c>
       <c r="D101" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E101" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G101" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C102">
         <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E102" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G102" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="B103" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C103">
         <v>1</v>
       </c>
       <c r="D103" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E103" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G103" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="B104" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E104" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G104" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="B105" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E105" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="G105" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="B106" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E106" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G106" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C107">
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E107" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G107" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="B108" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E108" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="G108" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="B109" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E109" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G109" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E110" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G110" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="B111" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="C111">
         <v>1</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E111" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="G111" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="B112" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E112" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="G112" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113">
-        <v>56</v>
+        <v>114</v>
       </c>
       <c r="B113" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C113">
         <v>1</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G113" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="B114" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C114">
         <v>1</v>
       </c>
       <c r="D114" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E114" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="G114" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="B115" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C115">
         <v>1</v>
       </c>
       <c r="D115" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E115" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="G115" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="B116" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C116">
         <v>1</v>
       </c>
       <c r="D116" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E116" t="s">
-        <v>391</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G116" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="B117" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C117">
         <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>395</v>
-      </c>
-      <c r="E117" t="s">
-        <v>396</v>
-      </c>
-      <c r="F117" s="1" t="s">
         <v>397</v>
       </c>
+      <c r="F117" s="2" t="s">
+        <v>398</v>
+      </c>
       <c r="G117" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="B118" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C118">
         <v>1</v>
       </c>
       <c r="D118" t="s">
-        <v>400</v>
-      </c>
-      <c r="E118" t="s">
         <v>401</v>
       </c>
+      <c r="F118" s="2" t="s">
+        <v>402</v>
+      </c>
       <c r="G118" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="B119" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C119">
         <v>1</v>
       </c>
       <c r="D119" t="s">
-        <v>404</v>
-      </c>
-      <c r="F119" s="4" t="s">
         <v>405</v>
       </c>
+      <c r="F119" s="2" t="s">
+        <v>406</v>
+      </c>
       <c r="G119" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>407</v>
@@ -5033,200 +5037,194 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120">
-        <v>63</v>
+        <v>121</v>
       </c>
       <c r="B120" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>408</v>
-      </c>
-      <c r="F120" s="4" t="s">
         <v>409</v>
       </c>
+      <c r="E120" t="s">
+        <v>410</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>411</v>
+      </c>
       <c r="G120" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>374</v>
+        <v>408</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D121" t="s">
-        <v>412</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
+      </c>
+      <c r="E121" t="s">
+        <v>415</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>416</v>
       </c>
       <c r="G121" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C122">
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E122" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G122" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E123" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G123" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C124">
         <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E124" t="s">
-        <v>427</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G124" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125">
-        <v>68</v>
+        <v>126</v>
       </c>
       <c r="B125" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
+        <v>433</v>
+      </c>
+      <c r="E125" t="s">
+        <v>434</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="G125" t="s">
         <v>431</v>
       </c>
-      <c r="E125" t="s">
-        <v>432</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="G125" t="s">
-        <v>434</v>
-      </c>
       <c r="H125" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="B126" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="C126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126" t="s">
-        <v>436</v>
-      </c>
-      <c r="E126" t="s">
-        <v>437</v>
-      </c>
-      <c r="G126" t="s">
         <v>438</v>
       </c>
-      <c r="H126" s="1" t="s">
+      <c r="F126" s="2" t="s">
         <v>439</v>
+      </c>
+      <c r="H126" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="B127" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="C127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D127" t="s">
-        <v>440</v>
-      </c>
-      <c r="E127" t="s">
         <v>441</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="F127" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="G127" t="s">
-        <v>438</v>
-      </c>
-      <c r="H127" s="1" t="s">
+      <c r="H127" t="s">
         <v>443</v>
       </c>
     </row>
@@ -5238,24 +5236,24 @@
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H4" r:id="rId1" display="中国政协网,http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="H77" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>
-    <hyperlink ref="F4" r:id="rId3" display="http://www.cppcc.gov.cn/images/favicon.ico"/>
-    <hyperlink ref="F60" r:id="rId4" display="http://www.chinadaily.com.cn/favicon.ico"/>
-    <hyperlink ref="F65" r:id="rId5" display="http://www.gmw.cn/favicon.ico"/>
-    <hyperlink ref="F75" r:id="rId6" display="https://www.cctv.com/favicon.ico"/>
-    <hyperlink ref="F76" r:id="rId7" display="http://www.cnr.cn/favicon.ico"/>
-    <hyperlink ref="F121" r:id="rId8" display="https://static.qr-code-scanner.io/favicon/180-1783679024.svg"/>
-    <hyperlink ref="F120" r:id="rId9" display="https://www.online-qr-scanner.com/favicon/favicon.ico"/>
-    <hyperlink ref="F119" r:id="rId10" display="https://static.clewm.net/static/images/favicon.ico"/>
-    <hyperlink ref="F10" r:id="rId11" display="http://www.nmgzx.gov.cn/favicon.ico"/>
-    <hyperlink ref="F18" r:id="rId12" display="https://www.gzzx.gov.cn/images/iconcf134.ico"/>
-    <hyperlink ref="F22" r:id="rId13" display="http://www.jpzx.gov.cn/favicon.ico"/>
-    <hyperlink ref="F33" r:id="rId14" display="https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/"/>
-    <hyperlink ref="F42" r:id="rId15" display="https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/"/>
-    <hyperlink ref="F45" r:id="rId16" display="https://www.hbzx.gov.cn/favicon.ico"/>
-    <hyperlink ref="F3" r:id="rId17" display="https://zhengxie.info/favicon.ico" tooltip="https://zhengxie.info/favicon.ico"/>
-    <hyperlink ref="F2" r:id="rId18" display="https://zhengxie.com.cn/assets/images/logo.svg" tooltip="https://zhengxie.com.cn/assets/images/logo.svg"/>
+    <hyperlink ref="H2" r:id="rId1" display="中国政协网,http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="H75" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>
+    <hyperlink ref="F2" r:id="rId3" display="http://www.cppcc.gov.cn/images/favicon.ico"/>
+    <hyperlink ref="F58" r:id="rId4" display="http://www.chinadaily.com.cn/favicon.ico"/>
+    <hyperlink ref="F63" r:id="rId5" display="http://www.gmw.cn/favicon.ico"/>
+    <hyperlink ref="F73" r:id="rId6" display="https://www.cctv.com/favicon.ico"/>
+    <hyperlink ref="F74" r:id="rId7" display="http://www.cnr.cn/favicon.ico"/>
+    <hyperlink ref="F119" r:id="rId8" display="https://static.qr-code-scanner.io/favicon/180-1783679024.svg"/>
+    <hyperlink ref="F118" r:id="rId9" display="https://www.online-qr-scanner.com/favicon/favicon.ico"/>
+    <hyperlink ref="F117" r:id="rId10" display="https://static.clewm.net/static/images/favicon.ico"/>
+    <hyperlink ref="F8" r:id="rId11" display="http://www.nmgzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="F16" r:id="rId12" display="https://www.gzzx.gov.cn/images/iconcf134.ico"/>
+    <hyperlink ref="F20" r:id="rId13" display="http://www.jpzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="F31" r:id="rId14" display="https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/"/>
+    <hyperlink ref="F40" r:id="rId15" display="https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/"/>
+    <hyperlink ref="F43" r:id="rId16" display="https://www.hbzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="F127" r:id="rId17" display="https://zhengxie.info/favicon.ico" tooltip="https://zhengxie.info/favicon.ico"/>
+    <hyperlink ref="F126" r:id="rId18" display="https://zhengxie.com.cn/assets/images/logo.svg" tooltip="https://zhengxie.com.cn/assets/images/logo.svg"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/assets/xlsx/links.xlsx
+++ b/assets/xlsx/links.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300" tabRatio="400"/>
+    <workbookView windowWidth="28800" windowHeight="11700" tabRatio="400"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$125</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="437">
   <si>
     <t>站序</t>
   </si>
@@ -1341,27 +1341,6 @@
   </si>
   <si>
     <t>官网,https://v.qq.com</t>
-  </si>
-  <si>
-    <t>正协</t>
-  </si>
-  <si>
-    <t>正协导航</t>
-  </si>
-  <si>
-    <t>https://zhengxie.com.cn/assets/images/logo.svg</t>
-  </si>
-  <si>
-    <t>正协导航,https://zhengxie.com.cn</t>
-  </si>
-  <si>
-    <t>正协信息</t>
-  </si>
-  <si>
-    <t>https://zhengxie.info/favicon.ico</t>
-  </si>
-  <si>
-    <t>正协信息,https://zhengxie.info</t>
   </si>
 </sst>
 </file>
@@ -2325,7 +2304,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.75" customWidth="1"/>
@@ -5188,49 +5167,9 @@
         <v>436</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
-      <c r="A126">
-        <v>1</v>
-      </c>
-      <c r="B126" t="s">
-        <v>437</v>
-      </c>
-      <c r="C126">
-        <v>1</v>
-      </c>
-      <c r="D126" t="s">
-        <v>438</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="H126" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
-      <c r="A127">
-        <v>1</v>
-      </c>
-      <c r="B127" t="s">
-        <v>437</v>
-      </c>
-      <c r="C127">
-        <v>1</v>
-      </c>
-      <c r="D127" t="s">
-        <v>441</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="H127" t="s">
-        <v>443</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H127" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:H127">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H125" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:H125">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -5252,8 +5191,6 @@
     <hyperlink ref="F31" r:id="rId14" display="https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/"/>
     <hyperlink ref="F40" r:id="rId15" display="https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/"/>
     <hyperlink ref="F43" r:id="rId16" display="https://www.hbzx.gov.cn/favicon.ico"/>
-    <hyperlink ref="F127" r:id="rId17" display="https://zhengxie.info/favicon.ico" tooltip="https://zhengxie.info/favicon.ico"/>
-    <hyperlink ref="F126" r:id="rId18" display="https://zhengxie.com.cn/assets/images/logo.svg" tooltip="https://zhengxie.com.cn/assets/images/logo.svg"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/assets/xlsx/links.xlsx
+++ b/assets/xlsx/links.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11700" tabRatio="400"/>
+    <workbookView windowWidth="28500" windowHeight="12660" tabRatio="400"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$H$129</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="448">
   <si>
     <t>站序</t>
   </si>
@@ -54,6 +54,39 @@
   </si>
   <si>
     <t>links</t>
+  </si>
+  <si>
+    <t>机构</t>
+  </si>
+  <si>
+    <t>中央网信办（国家互联网信息办公室）违法和不良信息举报中心</t>
+  </si>
+  <si>
+    <t>统筹协调全国互联网违法和不良信息举报工作；指导、监督各地各网站规范开展互联网违法和不良信息举报工作；受理、协助处置网民对互联网违法和不良信息的举报；宣传动员广大网民积极参与互联网违法和不良信息举报监督；主办中国互联网联合辟谣平台，统筹做好网络辟谣工作；开展国际交流合作，加强与境外国际组织、相关机构、互联网企业的联系，协调处理相关有害信息。</t>
+  </si>
+  <si>
+    <t>https://zhengxie.com.cn/assets/images/12377-3-08</t>
+  </si>
+  <si>
+    <t>首页,https://www.12377.cn/;机构简介,https://www.12377.cn/jgjj.html?tab=5</t>
+  </si>
+  <si>
+    <t>12321网络不良与垃圾信息举报受理中心</t>
+  </si>
+  <si>
+    <t>中国互联网协会受工业和信息化部委托设立的投诉受理机构。负责协助工业和信息化部承担关于互联网、移动电话网、固定电话网等各种形式信息通信网络及电信业务中不良与垃圾信息的投诉受理、线索转办及信息统计等工作。</t>
+  </si>
+  <si>
+    <t>https://www.12321.cn/Public/home/image/favicon.ico</t>
+  </si>
+  <si>
+    <t>首页,https://www.12321.cn/;机构介绍,https://www.12321.cn/single?tpl=institution</t>
+  </si>
+  <si>
+    <t>https://zhengxie.com.cn/assets/images/12377-3-07</t>
+  </si>
+  <si>
+    <t>https://zhengxie.com.cn/assets/images/12377-3-04</t>
   </si>
   <si>
     <t>政协</t>
@@ -1954,9 +1987,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2304,14 +2338,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.75" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="7.875" customWidth="1"/>
     <col min="4" max="4" width="16.75" customWidth="1"/>
-    <col min="5" max="5" width="8.5" customWidth="1"/>
+    <col min="5" max="5" width="27.125" customWidth="1"/>
     <col min="6" max="6" width="15.125" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.375" customWidth="1"/>
     <col min="8" max="8" width="32.125" style="1" customWidth="1"/>
@@ -2345,7 +2379,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -2359,7 +2393,7 @@
       <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -2368,7 +2402,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -2379,60 +2413,70 @@
       <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="H3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4"/>
       <c r="H4" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
+      <c r="G5"/>
       <c r="H5" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2440,210 +2484,211 @@
       <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
-        <v>14</v>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" t="s">
         <v>34</v>
       </c>
-      <c r="G12" t="s">
-        <v>35</v>
-      </c>
       <c r="H12" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="2" t="s">
         <v>45</v>
       </c>
       <c r="G16" t="s">
@@ -2655,10 +2700,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -2675,10 +2720,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2695,10 +2740,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -2715,10 +2760,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -2726,7 +2771,7 @@
       <c r="D20" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>56</v>
       </c>
       <c r="G20" t="s">
@@ -2738,10 +2783,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -2750,7 +2795,7 @@
         <v>59</v>
       </c>
       <c r="G21" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>60</v>
@@ -2758,10 +2803,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -2770,7 +2815,7 @@
         <v>61</v>
       </c>
       <c r="G22" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>62</v>
@@ -2778,10 +2823,10 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2790,416 +2835,413 @@
         <v>63</v>
       </c>
       <c r="G23" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="G24" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G25" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G26" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G32" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G33" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>88</v>
+        <v>90</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="G35" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G37" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G38" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G39" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G40" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G41" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G42" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>106</v>
-      </c>
-      <c r="F43" s="2" t="s">
         <v>107</v>
       </c>
       <c r="G43" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>108</v>
@@ -3207,10 +3249,10 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -3218,291 +3260,294 @@
       <c r="D44" t="s">
         <v>109</v>
       </c>
+      <c r="F44" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="G44" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
+        <v>112</v>
+      </c>
+      <c r="G45" t="s">
         <v>46</v>
       </c>
-      <c r="B45" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45" t="s">
-        <v>111</v>
-      </c>
-      <c r="G45" t="s">
-        <v>35</v>
-      </c>
       <c r="H45" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G46" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>115</v>
+        <v>117</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="G47" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G48" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G49" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G50" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G51" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G52" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C53">
         <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G53" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G55" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G56" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G57" t="s">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B58" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="D58" t="s">
-        <v>139</v>
-      </c>
-      <c r="F58" s="1" t="s">
         <v>140</v>
       </c>
       <c r="G58" t="s">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>141</v>
@@ -3510,10 +3555,10 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B59" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -3522,7 +3567,7 @@
         <v>142</v>
       </c>
       <c r="G59" t="s">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>143</v>
@@ -3530,10 +3575,10 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -3542,7 +3587,7 @@
         <v>144</v>
       </c>
       <c r="G60" t="s">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>145</v>
@@ -3550,132 +3595,126 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>146</v>
-      </c>
-      <c r="E61" t="s">
         <v>147</v>
       </c>
-      <c r="F61" s="2"/>
       <c r="G61" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B62" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>149</v>
+        <v>150</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="G62" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C63">
         <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>151</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G63" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
       <c r="D64" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G64" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C65">
         <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E65" t="s">
-        <v>157</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="F65" s="3"/>
       <c r="G65" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>159</v>
-      </c>
-      <c r="E66" t="s">
         <v>160</v>
       </c>
       <c r="G66" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>161</v>
@@ -3683,10 +3722,10 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -3694,11 +3733,11 @@
       <c r="D67" t="s">
         <v>162</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G67" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>164</v>
@@ -3706,10 +3745,10 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B68" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -3717,77 +3756,77 @@
       <c r="D68" t="s">
         <v>165</v>
       </c>
-      <c r="E68" t="s">
+      <c r="G68" t="s">
+        <v>148</v>
+      </c>
+      <c r="H68" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="G68" t="s">
-        <v>137</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C69">
         <v>1</v>
       </c>
       <c r="D69" t="s">
+        <v>167</v>
+      </c>
+      <c r="E69" t="s">
         <v>168</v>
       </c>
-      <c r="E69" t="s">
+      <c r="G69" t="s">
+        <v>148</v>
+      </c>
+      <c r="H69" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="G69" t="s">
-        <v>137</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B70" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C70">
         <v>1</v>
       </c>
       <c r="D70" t="s">
+        <v>170</v>
+      </c>
+      <c r="E70" t="s">
         <v>171</v>
       </c>
-      <c r="E70" t="s">
+      <c r="G70" t="s">
+        <v>148</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="G70" t="s">
-        <v>137</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B71" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="s">
+        <v>173</v>
+      </c>
+      <c r="E71" t="s">
         <v>174</v>
       </c>
       <c r="G71" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>175</v>
@@ -3795,10 +3834,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -3810,7 +3849,7 @@
         <v>177</v>
       </c>
       <c r="G72" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>178</v>
@@ -3818,10 +3857,10 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -3829,11 +3868,12 @@
       <c r="D73" t="s">
         <v>179</v>
       </c>
-      <c r="F73" s="2" t="s">
+      <c r="E73" t="s">
         <v>180</v>
       </c>
+      <c r="F73" s="1"/>
       <c r="G73" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>181</v>
@@ -3841,10 +3881,10 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B74" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -3852,11 +3892,12 @@
       <c r="D74" t="s">
         <v>182</v>
       </c>
-      <c r="F74" s="2" t="s">
+      <c r="E74" t="s">
         <v>183</v>
       </c>
+      <c r="F74" s="1"/>
       <c r="G74" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>184</v>
@@ -3864,1333 +3905,1431 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B75" t="s">
+        <v>146</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75" t="s">
         <v>185</v>
       </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="G75" t="s">
+        <v>148</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="E75" t="s">
-        <v>187</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G75" t="s">
-        <v>189</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B76" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E76" t="s">
-        <v>192</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>193</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="F76" s="1"/>
       <c r="G76" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B77" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>196</v>
-      </c>
-      <c r="E77" t="s">
-        <v>197</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>198</v>
+        <v>190</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="G77" t="s">
-        <v>199</v>
+        <v>148</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B78" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>201</v>
-      </c>
-      <c r="E78" t="s">
-        <v>202</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>203</v>
+        <v>193</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="G78" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B79" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="E79" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="G79" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B80" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E80" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="G80" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B81" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="E81" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="G81" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B82" t="s">
+        <v>196</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82" t="s">
+        <v>212</v>
+      </c>
+      <c r="E82" t="s">
+        <v>213</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G82" t="s">
+        <v>215</v>
+      </c>
+      <c r="H82" s="1" t="s">
         <v>216</v>
-      </c>
-      <c r="C82">
-        <v>1</v>
-      </c>
-      <c r="D82" t="s">
-        <v>222</v>
-      </c>
-      <c r="E82" t="s">
-        <v>223</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G82" t="s">
-        <v>225</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B83" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C83">
         <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="E83" t="s">
-        <v>228</v>
+        <v>218</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="G83" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B84" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C84">
         <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="E84" t="s">
-        <v>232</v>
+        <v>223</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="G84" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B85" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E85" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="G85" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B86" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E86" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G86" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B87" t="s">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>144</v>
+        <v>238</v>
       </c>
       <c r="E87" t="s">
-        <v>245</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>246</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="F87" s="1"/>
       <c r="G87" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B88" t="s">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E88" t="s">
-        <v>250</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>251</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="F88" s="1"/>
       <c r="G88" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B89" t="s">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E89" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="G89" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B90" t="s">
-        <v>135</v>
+        <v>227</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E90" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="G90" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B91" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C91">
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>264</v>
+        <v>155</v>
       </c>
       <c r="E91" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="G91" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B92" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="E92" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="G92" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B93" t="s">
-        <v>274</v>
+        <v>146</v>
       </c>
       <c r="C93">
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="E93" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="G93" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B94" t="s">
+        <v>146</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+      <c r="D94" t="s">
+        <v>270</v>
+      </c>
+      <c r="E94" t="s">
+        <v>271</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G94" t="s">
+        <v>273</v>
+      </c>
+      <c r="H94" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="C94">
-        <v>3</v>
-      </c>
-      <c r="D94" t="s">
-        <v>280</v>
-      </c>
-      <c r="E94" t="s">
-        <v>281</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="G94" t="s">
-        <v>283</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B95" t="s">
-        <v>274</v>
+        <v>146</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="E95" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="G95" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B96" t="s">
-        <v>274</v>
+        <v>146</v>
       </c>
       <c r="C96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D96" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="E96" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="G96" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B97" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="E97" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="G97" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B98" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="E98" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="G98" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B99" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="E99" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="G99" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B100" t="s">
+        <v>285</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100" t="s">
+        <v>301</v>
+      </c>
+      <c r="E100" t="s">
+        <v>302</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="G100" t="s">
+        <v>304</v>
+      </c>
+      <c r="H100" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="C100">
-        <v>1</v>
-      </c>
-      <c r="D100" t="s">
-        <v>311</v>
-      </c>
-      <c r="E100" t="s">
-        <v>312</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G100" t="s">
-        <v>314</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B101" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="E101" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="G101" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B102" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="E102" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="G102" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B103" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C103">
         <v>1</v>
       </c>
       <c r="D103" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="E103" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="G103" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B104" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="E104" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="G104" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B105" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="E105" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="G105" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B106" t="s">
+        <v>316</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="D106" t="s">
+        <v>332</v>
+      </c>
+      <c r="E106" t="s">
+        <v>333</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G106" t="s">
+        <v>335</v>
+      </c>
+      <c r="H106" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="C106">
-        <v>2</v>
-      </c>
-      <c r="D106" t="s">
-        <v>342</v>
-      </c>
-      <c r="E106" t="s">
-        <v>343</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="G106" t="s">
-        <v>345</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D107" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E107" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="G107" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B108" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="C108">
         <v>1</v>
       </c>
       <c r="D108" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="E108" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="G108" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B109" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="E109" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="G109" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B110" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="C110">
         <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="E110" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="G110" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B111" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="E111" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="G111" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B112" t="s">
+        <v>347</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112" t="s">
+        <v>363</v>
+      </c>
+      <c r="E112" t="s">
+        <v>364</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G112" t="s">
+        <v>366</v>
+      </c>
+      <c r="H112" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="C112">
-        <v>1</v>
-      </c>
-      <c r="D112" t="s">
-        <v>373</v>
-      </c>
-      <c r="E112" t="s">
-        <v>374</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="G112" t="s">
-        <v>376</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B113" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C113">
         <v>1</v>
       </c>
       <c r="D113" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E113" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G113" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B114" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="E114" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="G114" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B115" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="C115">
         <v>1</v>
       </c>
       <c r="D115" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="E115" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="G115" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B116" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="C116">
         <v>1</v>
       </c>
       <c r="D116" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="E116" t="s">
-        <v>394</v>
+        <v>385</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="G116" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B117" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="C117">
         <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>397</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>398</v>
+        <v>389</v>
+      </c>
+      <c r="E117" t="s">
+        <v>390</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>391</v>
       </c>
       <c r="G117" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B118" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="C118">
         <v>1</v>
       </c>
       <c r="D118" t="s">
-        <v>401</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
+      </c>
+      <c r="E118" t="s">
+        <v>395</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="G118" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B119" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="C119">
         <v>1</v>
       </c>
       <c r="D119" t="s">
-        <v>405</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>406</v>
+        <v>399</v>
+      </c>
+      <c r="E119" t="s">
+        <v>400</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="G119" t="s">
+        <v>402</v>
+      </c>
+      <c r="H119" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B120" t="s">
-        <v>408</v>
+        <v>378</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D120" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="E120" t="s">
-        <v>410</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>411</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="F120" s="1"/>
       <c r="G120" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B121" t="s">
+        <v>378</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+      <c r="D121" t="s">
         <v>408</v>
       </c>
-      <c r="C121">
-        <v>2</v>
-      </c>
-      <c r="D121" t="s">
-        <v>414</v>
-      </c>
-      <c r="E121" t="s">
-        <v>415</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>416</v>
+      <c r="F121" s="3" t="s">
+        <v>409</v>
       </c>
       <c r="G121" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B122" t="s">
-        <v>408</v>
+        <v>378</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D122" t="s">
-        <v>419</v>
-      </c>
-      <c r="E122" t="s">
-        <v>420</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>421</v>
+        <v>412</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>413</v>
       </c>
       <c r="G122" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B123" t="s">
-        <v>408</v>
+        <v>378</v>
       </c>
       <c r="C123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D123" t="s">
-        <v>424</v>
-      </c>
-      <c r="E123" t="s">
-        <v>425</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>426</v>
+        <v>416</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>417</v>
       </c>
       <c r="G123" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B124" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="C124">
         <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="E124" t="s">
-        <v>430</v>
+        <v>421</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>422</v>
       </c>
       <c r="G124" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B125" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
+        <v>425</v>
+      </c>
+      <c r="E125" t="s">
+        <v>426</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="G125" t="s">
+        <v>428</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126">
+        <v>123</v>
+      </c>
+      <c r="B126" t="s">
+        <v>419</v>
+      </c>
+      <c r="C126">
+        <v>2</v>
+      </c>
+      <c r="D126" t="s">
+        <v>430</v>
+      </c>
+      <c r="E126" t="s">
+        <v>431</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G126" t="s">
         <v>433</v>
       </c>
-      <c r="E125" t="s">
+      <c r="H126" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="F125" s="1" t="s">
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127">
+        <v>124</v>
+      </c>
+      <c r="B127" t="s">
+        <v>419</v>
+      </c>
+      <c r="C127">
+        <v>2</v>
+      </c>
+      <c r="D127" t="s">
         <v>435</v>
       </c>
-      <c r="G125" t="s">
-        <v>431</v>
-      </c>
-      <c r="H125" s="1" t="s">
+      <c r="E127" t="s">
         <v>436</v>
       </c>
+      <c r="F127" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="G127" t="s">
+        <v>438</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="128" customFormat="1" spans="1:8">
+      <c r="A128">
+        <v>125</v>
+      </c>
+      <c r="B128" t="s">
+        <v>419</v>
+      </c>
+      <c r="C128">
+        <v>2</v>
+      </c>
+      <c r="D128" t="s">
+        <v>440</v>
+      </c>
+      <c r="E128" t="s">
+        <v>441</v>
+      </c>
+      <c r="F128" s="1"/>
+      <c r="G128" t="s">
+        <v>442</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="129" customFormat="1" spans="1:8">
+      <c r="A129">
+        <v>126</v>
+      </c>
+      <c r="B129" t="s">
+        <v>419</v>
+      </c>
+      <c r="C129">
+        <v>2</v>
+      </c>
+      <c r="D129" t="s">
+        <v>444</v>
+      </c>
+      <c r="E129" t="s">
+        <v>445</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="G129" t="s">
+        <v>442</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>447</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H125" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:H125">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H129" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:H129">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" display="中国政协网,http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="H75" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>
-    <hyperlink ref="F2" r:id="rId3" display="http://www.cppcc.gov.cn/images/favicon.ico"/>
-    <hyperlink ref="F58" r:id="rId4" display="http://www.chinadaily.com.cn/favicon.ico"/>
-    <hyperlink ref="F63" r:id="rId5" display="http://www.gmw.cn/favicon.ico"/>
-    <hyperlink ref="F73" r:id="rId6" display="https://www.cctv.com/favicon.ico"/>
-    <hyperlink ref="F74" r:id="rId7" display="http://www.cnr.cn/favicon.ico"/>
-    <hyperlink ref="F119" r:id="rId8" display="https://static.qr-code-scanner.io/favicon/180-1783679024.svg"/>
-    <hyperlink ref="F118" r:id="rId9" display="https://www.online-qr-scanner.com/favicon/favicon.ico"/>
-    <hyperlink ref="F117" r:id="rId10" display="https://static.clewm.net/static/images/favicon.ico"/>
-    <hyperlink ref="F8" r:id="rId11" display="http://www.nmgzx.gov.cn/favicon.ico"/>
-    <hyperlink ref="F16" r:id="rId12" display="https://www.gzzx.gov.cn/images/iconcf134.ico"/>
-    <hyperlink ref="F20" r:id="rId13" display="http://www.jpzx.gov.cn/favicon.ico"/>
-    <hyperlink ref="F31" r:id="rId14" display="https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/"/>
-    <hyperlink ref="F40" r:id="rId15" display="https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/"/>
-    <hyperlink ref="F43" r:id="rId16" display="https://www.hbzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="H6" r:id="rId1" display="中国政协网,http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="H79" r:id="rId2" display="官网,https://www.baidu.com;百度百科,https://baike.baidu.com;地图,https://map.baidu.com"/>
+    <hyperlink ref="F6" r:id="rId3" display="http://www.cppcc.gov.cn/images/favicon.ico"/>
+    <hyperlink ref="F62" r:id="rId4" display="http://www.chinadaily.com.cn/favicon.ico"/>
+    <hyperlink ref="F67" r:id="rId5" display="http://www.gmw.cn/favicon.ico"/>
+    <hyperlink ref="F77" r:id="rId6" display="https://www.cctv.com/favicon.ico"/>
+    <hyperlink ref="F78" r:id="rId7" display="http://www.cnr.cn/favicon.ico"/>
+    <hyperlink ref="F123" r:id="rId8" display="https://static.qr-code-scanner.io/favicon/180-1783679024.svg"/>
+    <hyperlink ref="F122" r:id="rId9" display="https://www.online-qr-scanner.com/favicon/favicon.ico"/>
+    <hyperlink ref="F121" r:id="rId10" display="https://static.clewm.net/static/images/favicon.ico"/>
+    <hyperlink ref="F12" r:id="rId11" display="http://www.nmgzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="F20" r:id="rId12" display="https://www.gzzx.gov.cn/images/iconcf134.ico"/>
+    <hyperlink ref="F24" r:id="rId13" display="http://www.jpzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="F35" r:id="rId14" display="https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/"/>
+    <hyperlink ref="F44" r:id="rId15" display="https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/"/>
+    <hyperlink ref="F47" r:id="rId16" display="https://www.hbzx.gov.cn/favicon.ico"/>
+    <hyperlink ref="F3" r:id="rId17" display="https://www.12321.cn/Public/home/image/favicon.ico"/>
+    <hyperlink ref="F2" r:id="rId18" display="https://zhengxie.com.cn/assets/images/12377-3-08" tooltip="https://zhengxie.com.cn/assets/images/12377-3-08"/>
+    <hyperlink ref="F4" r:id="rId19" display="https://zhengxie.com.cn/assets/images/12377-3-07" tooltip="https://zhengxie.com.cn/assets/images/12377-3-07"/>
+    <hyperlink ref="F5" r:id="rId20" display="https://zhengxie.com.cn/assets/images/12377-3-04" tooltip="https://zhengxie.com.cn/assets/images/12377-3-04"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/assets/xlsx/links.xlsx
+++ b/assets/xlsx/links.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28500" windowHeight="12660" tabRatio="400"/>
+    <workbookView windowWidth="28500" windowHeight="11700" tabRatio="400"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
     <t>统筹协调全国互联网违法和不良信息举报工作；指导、监督各地各网站规范开展互联网违法和不良信息举报工作；受理、协助处置网民对互联网违法和不良信息的举报；宣传动员广大网民积极参与互联网违法和不良信息举报监督；主办中国互联网联合辟谣平台，统筹做好网络辟谣工作；开展国际交流合作，加强与境外国际组织、相关机构、互联网企业的联系，协调处理相关有害信息。</t>
   </si>
   <si>
-    <t>https://zhengxie.com.cn/assets/images/12377-3-08</t>
+    <t>https://zhengxie.com.cn/assets/images/12377-3-08.png</t>
   </si>
   <si>
     <t>首页,https://www.12377.cn/;机构简介,https://www.12377.cn/jgjj.html?tab=5</t>
@@ -83,10 +83,10 @@
     <t>首页,https://www.12321.cn/;机构介绍,https://www.12321.cn/single?tpl=institution</t>
   </si>
   <si>
-    <t>https://zhengxie.com.cn/assets/images/12377-3-07</t>
-  </si>
-  <si>
-    <t>https://zhengxie.com.cn/assets/images/12377-3-04</t>
+    <t>https://zhengxie.com.cn/assets/images/12377-3-07.png</t>
+  </si>
+  <si>
+    <t>https://zhengxie.com.cn/assets/images/12377-3-04.png</t>
   </si>
   <si>
     <t>政协</t>
@@ -1990,7 +1990,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2442,7 +2442,6 @@
       <c r="F4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G4"/>
       <c r="H4" s="1" t="s">
         <v>12</v>
       </c>
@@ -2466,7 +2465,6 @@
       <c r="F5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G5"/>
       <c r="H5" s="1" t="s">
         <v>12</v>
       </c>
@@ -3871,7 +3869,6 @@
       <c r="E73" t="s">
         <v>180</v>
       </c>
-      <c r="F73" s="1"/>
       <c r="G73" t="s">
         <v>148</v>
       </c>
@@ -3895,7 +3892,6 @@
       <c r="E74" t="s">
         <v>183</v>
       </c>
-      <c r="F74" s="1"/>
       <c r="G74" t="s">
         <v>148</v>
       </c>
@@ -3939,7 +3935,6 @@
       <c r="E76" t="s">
         <v>188</v>
       </c>
-      <c r="F76" s="1"/>
       <c r="G76" t="s">
         <v>148</v>
       </c>
@@ -4217,7 +4212,6 @@
       <c r="E87" t="s">
         <v>239</v>
       </c>
-      <c r="F87" s="1"/>
       <c r="G87" t="s">
         <v>240</v>
       </c>
@@ -4241,7 +4235,6 @@
       <c r="E88" t="s">
         <v>243</v>
       </c>
-      <c r="F88" s="1"/>
       <c r="G88" t="s">
         <v>244</v>
       </c>
@@ -5071,7 +5064,6 @@
       <c r="E120" t="s">
         <v>405</v>
       </c>
-      <c r="F120" s="1"/>
       <c r="G120" t="s">
         <v>406</v>
       </c>
@@ -5304,7 +5296,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H129" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:H129">
+    <sortState ref="A1:H129">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -5326,10 +5318,10 @@
     <hyperlink ref="F35" r:id="rId14" display="https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/"/>
     <hyperlink ref="F44" r:id="rId15" display="https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/"/>
     <hyperlink ref="F47" r:id="rId16" display="https://www.hbzx.gov.cn/favicon.ico"/>
-    <hyperlink ref="F3" r:id="rId17" display="https://www.12321.cn/Public/home/image/favicon.ico"/>
-    <hyperlink ref="F2" r:id="rId18" display="https://zhengxie.com.cn/assets/images/12377-3-08" tooltip="https://zhengxie.com.cn/assets/images/12377-3-08"/>
-    <hyperlink ref="F4" r:id="rId19" display="https://zhengxie.com.cn/assets/images/12377-3-07" tooltip="https://zhengxie.com.cn/assets/images/12377-3-07"/>
-    <hyperlink ref="F5" r:id="rId20" display="https://zhengxie.com.cn/assets/images/12377-3-04" tooltip="https://zhengxie.com.cn/assets/images/12377-3-04"/>
+    <hyperlink ref="F3" r:id="rId17" display="https://www.12321.cn/Public/home/image/favicon.ico" tooltip="https://www.12321.cn/Public/home/image/favicon.ico"/>
+    <hyperlink ref="F2" r:id="rId18" display="https://zhengxie.com.cn/assets/images/12377-3-08.png" tooltip="https://zhengxie.com.cn/assets/images/12377-3-08.png"/>
+    <hyperlink ref="F4" r:id="rId19" display="https://zhengxie.com.cn/assets/images/12377-3-07.png" tooltip="https://zhengxie.com.cn/assets/images/12377-3-07.png"/>
+    <hyperlink ref="F5" r:id="rId20" display="https://zhengxie.com.cn/assets/images/12377-3-04.png" tooltip="https://zhengxie.com.cn/assets/images/12377-3-04.png"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
